--- a/deliverables/GIZMo_ZedBoard_DCS_Intake.xlsx
+++ b/deliverables/GIZMo_ZedBoard_DCS_Intake.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tag List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tag List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tag List'!$A$1:$AA$75</definedName>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="B1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Draft 0.7 requirements intake for joint GIZMo / Slow Controls review</t>
+          <t>Draft 0.8 requirements intake for joint GIZMo / Slow Controls review</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Kria values use the retained 2026-07-27..2026-08-03 permanent SQLite replica as observational evidence. Legacy values use 15 direct coherent frames from the connected ZedBoard on 2026-08-12 plus 27 contiguous deployed-adapter cycles on 2026-08-13; target communication was lost before the 100-cycle acceptance run completed. These sources refine nominal/desired fields but do not replace approved alarm or metrology limits.</t>
+          <t>Kria values use the retained 2026-07-27..2026-08-03 permanent SQLite replica as observational evidence. Legacy values use 15 direct coherent frames from the connected ZedBoard on 2026-08-12 plus 27 contiguous validation-adapter cycles on 2026-08-13; target communication was lost before the 100-cycle acceptance run completed. These sources refine nominal/desired fields but do not replace approved alarm or metrology limits.</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Installed GIZMo runtime or adapter version.</t>
+          <t>Installed legacy GIZMo OPC UA server version.</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Linux boot identifier of the modern host running the off-board OPC UA adapter.</t>
+          <t>Linux boot identifier of the target or reviewed host running the legacy OPC UA server.</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="AA30" s="13" t="inlineStr">
         <is>
-          <t>A target reboot, GIZMO.elf PID/hash change, or adapter restart opens a new Ignition history epoch; it does not change the meaning of this node.</t>
+          <t>A target reboot, GIZMO.elf PID/hash change, or server restart opens a new Ignition history epoch; it does not change the meaning of this node.</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>Off-board adapter receive time until legacy target time is synchronized; status remains uncertain when substituted.</t>
+          <t>Legacy server receive time until target time is synchronized; status remains uncertain when substituted.</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>Legacy Adapter</t>
+          <t>Legacy OPC UA Server</t>
         </is>
       </c>
       <c r="B57" s="15" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Version of the off-board legacy acquisition and allow-listed command adapter.</t>
+          <t>Version of the legacy OPC UA server.</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AA57" s="15" t="inlineStr">
         <is>
-          <t>The initial pilot implementation is read-only; mutating capabilities below are requirements for staged commissioning, not claims about today's adapter.</t>
+          <t>The production server is under development and its initial release is read-only. The earlier off-board adapter is validation evidence; mutating capabilities below remain staged requirements.</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="AA67" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the off-board adapter or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="AA68" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the off-board adapter or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="AA69" s="15" t="inlineStr">
         <is>
-          <t>Quality refers to the off-board adapter or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="AA70" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the off-board adapter or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AA71" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the off-board adapter or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AA72" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the off-board adapter or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Aggregate quality of owned services or adapter processes.</t>
+          <t>Aggregate quality of owned legacy OPC UA server processes.</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AA73" s="15" t="inlineStr">
         <is>
-          <t>Quality refers to the off-board adapter or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AA74" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the off-board adapter or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="AA75" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the off-board adapter or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>

--- a/deliverables/GIZMo_ZedBoard_DCS_Intake.xlsx
+++ b/deliverables/GIZMo_ZedBoard_DCS_Intake.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tag List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tag List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tag List'!$A$1:$AA$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tag List'!$A$1:$AA$78</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tag List'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Tag List'!$A$1:$AA$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Tag List'!$A$1:$AA$78</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C41"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>opc.tcp://&lt;assigned-host&gt;:4840 (final host/IP assigned by Slow Controls)</t>
+          <t>opc.tcp://&lt;assigned-host&gt;:4842 (final production host/IP assigned by Slow Controls)</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Draft 0.8 requirements intake for joint GIZMo / Slow Controls review</t>
+          <t>Draft 0.9 requirements intake for joint GIZMo / Slow Controls review</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Kria values use the retained 2026-07-27..2026-08-03 permanent SQLite replica as observational evidence. Legacy values use 15 direct coherent frames from the connected ZedBoard on 2026-08-12 plus 27 contiguous validation-adapter cycles on 2026-08-13; target communication was lost before the 100-cycle acceptance run completed. These sources refine nominal/desired fields but do not replace approved alarm or metrology limits.</t>
+          <t>Kria values use the retained 2026-07-27..2026-08-03 permanent SQLite replica as observational evidence. Legacy values use 15 direct coherent frames from 2026-08-12, 27 contiguous adapter-pilot cycles, and the 2026-08-13 native-server authenticated 100-Ohm idempotent write/readback. The full 100-cycle physical-display acceptance remains open. These sources refine nominal/desired fields but do not replace approved alarm or metrology limits.</t>
         </is>
       </c>
     </row>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I2" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="19" t="n">
-        <v>500</v>
+        <v>1023</v>
       </c>
       <c r="K2" s="19" t="n">
         <v>100</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AA2" s="21" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL, COMMISSIONING STAGE 2; the initial pilot shall reject writes until released. OPC UA UInt32, restricted by documented legacy policy to integer 1..500 Ohm. Requested initial/normal setpoint is 100 Ohm, matching the connected controller. Map only to allow-listed set_th N, serialize access, read back the controller/display value, audit, and fault-lock on mismatch.</t>
+          <t>IMPLEMENTED NATIVE CONTROL. Authenticated OPC UA UInt32 range is 0..1023 Ohm; anonymous writes are denied and the initial normal/operator band is 1..500 Ohm. Requested initial setpoint is 100 Ohm. Each write requires fresh exact controller identity and agreement among journal, persistent file, and live word; it atomically persists the value, updates/readbacks controller memory, sends the recovered display transaction, resumes the same PID, and reports Configuration.LastCommandResult. On 2026-08-13 the native ARMv7 OPC UA server was deployed on the ZedBoard at TCP 4842 with target-local recovery buffering and automatic time synchronization. Anonymous sessions are read-only. An authenticated, idempotent 100-Ohm ThresholdOhm write passed persistent-file, live controller word, recovery-journal, and display-transaction readback without changing the controller or recovery process identity. Other configuration writes and all Methods remain explicitly unsupported.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AA3" s="21" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL, COMMISSIONING STAGE 1; the initial pilot shall reject writes until released. OPC UA UInt32. The live SysV service starts GIZMO.elf with argument 3 and the engineering note documents RUN default 3 seconds. Keep the initial value fixed at 3 until an upper bound and alternate cadences are commissioned.</t>
+          <t>REQUIRED FUTURE CONTROL, COMMISSIONING STAGE 1; the deployed native endpoint does not expose this node and rejects every non-threshold write. OPC UA UInt32 is requested. The live SysV service starts GIZMO.elf with argument 3 and the engineering note documents RUN default 3 seconds. Keep the initial value fixed at 3 until an upper bound, update mechanism, and alternate cadences are commissioned.</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       <c r="Z6" s="23" t="n"/>
       <c r="AA6" s="25" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL, COMMISSIONING STAGE 3, MAINTENANCE-ONLY. OPC UA Method: absolute DateTime input; String acceptance result. Map only to reviewed set_time behavior; verify Time.CurrentUtc/Quality and log the clock step.</t>
+          <t>MAINTENANCE FALLBACK, NOT NORMAL SYNCHRONIZATION. The automatic target SNTP client is the approved normal path. Keep this method disabled unless automatic recovery has failed and a reviewed maintenance procedure authorizes a one-time step; it must not assert NtpSynchronized.</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Installed legacy GIZMo OPC UA server version.</t>
+          <t>Installed GIZMo runtime or adapter version.</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Linux boot identifier of the target or reviewed host running the legacy OPC UA server.</t>
+          <t>Linux boot identifier of the legacy ZedBoard that runs the native OPC UA endpoint.</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="AA30" s="13" t="inlineStr">
         <is>
-          <t>A target reboot, GIZMO.elf PID/hash change, or server restart opens a new Ignition history epoch; it does not change the meaning of this node.</t>
+          <t>A target reboot, GIZMO.elf PID/hash change, or native server restart opens a new Ignition history epoch; it does not change the meaning of this node.</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>Legacy server receive time until target time is synchronized; status remains uncertain when substituted.</t>
+          <t>Target-local recovery-record source time; quality is non-good whenever current-boot target synchronization evidence is unavailable or stale.</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AA36" s="13" t="inlineStr">
         <is>
-          <t>Documented legacy presentation range is 0..500 Ohm; values above 500 are HIGH Z. The controller's internal estimate is mathematically clamped at 999 Ohm, but 999 is not a physical span endpoint. The installed CT/inductor calibration is not yet revalidated. The current connected electronics-only setup produced 111.554..111.902 Ohm across 15 coherent completed RUN frames and the screen displayed 112 Ohm/green. Nominal 112 is therefore a dated live observation, not a detector-loop target. The requested finite normal band is 100..500 Ohm; HIGH Z is also normal. Do not configure a second independent ResistanceOhm comparison once authoritative Alarm.Active is available. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits. The deployed read-only adapter then captured 27 contiguous cycles (Sequence 21..47) on 2026-08-13: 111.465703..112.010978 Ohm, mean 111.722419 Ohm, and exactly 100 Ohm threshold; the calculated legacy display-equivalent rounding was 112 Ohm in 26 cycles and 111 Ohm in one. The samples carried UncertainLastUsableValue and Measurement.Quality=Uncertain, consistent with the unvalidated legacy measurement path. Target communication was lost before the requested 100 cycles completed, so this is additional commissioning evidence, not acceptance.</t>
+          <t>Documented legacy presentation range is 0..500 Ohm; values above 500 are HIGH Z. The controller's internal estimate is mathematically clamped at 999 Ohm, but 999 is not a physical span endpoint. The installed CT/inductor calibration is not yet revalidated. The current connected electronics-only setup produced 111.554..111.902 Ohm across 15 coherent completed RUN frames and the screen displayed 112 Ohm/green. Nominal 112 is therefore a dated live observation, not a detector-loop target. The requested finite normal band is 100..500 Ohm; HIGH Z is also normal. Do not configure a second independent ResistanceOhm comparison once authoritative Alarm.Active is available. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits. The deployed read-only adapter then captured 27 contiguous cycles (Sequence 21..47) on 2026-08-13: 111.465703..112.010978 Ohm, mean 111.722419 Ohm, and exactly 100 Ohm threshold; the calculated legacy display-equivalent rounding was 112 Ohm in 26 cycles and 111 Ohm in one. The samples carried UncertainLastUsableValue and Measurement.Quality=Uncertain, consistent with the unvalidated legacy measurement path. Target communication was lost before the requested 100 cycles completed, so this is additional commissioning evidence, not acceptance.</t>
         </is>
       </c>
     </row>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>500</v>
+        <v>1023</v>
       </c>
       <c r="K40" s="14" t="n">
         <v>100</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AA40" s="13" t="inlineStr">
         <is>
-          <t>Live global_th readback was exactly 100 Ohm in every one of 15 coherent completed RUN frames on 2026-08-12 and every one of 27 deployed-adapter pilot cycles on 2026-08-13. Use 100 Ohm as the requested initial setpoint. The display wire field is 10 bits, but the documented legacy threshold operating range is integer 1..500 Ohm.</t>
+          <t>Live global_th readback was exactly 100 Ohm in every one of 15 coherent completed RUN frames on 2026-08-12, every one of 27 adapter-pilot cycles, and the native-server control acceptance on 2026-08-13. Use 100 Ohm as the requested initial setpoint. The recovered display/controller field and authenticated OPC UA implementation accept UInt32 values 0..1023 Ohm; the initial normal/operator band remains 1..500 Ohm. On 2026-08-13 the native ARMv7 OPC UA server was deployed on the ZedBoard at TCP 4842 with target-local recovery buffering and automatic time synchronization. Anonymous sessions are read-only. An authenticated, idempotent 100-Ohm ThresholdOhm write passed persistent-file, live controller word, recovery-journal, and display-transaction readback without changing the controller or recovery process identity. Other configuration writes and all Methods remain explicitly unsupported.</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="AA43" s="13" t="inlineStr">
         <is>
-          <t>Live controller magnitude was 219.494..219.924 across 15 coherent completed RUN frames. The 219..221 desired band is a provisional same-setup trend envelope, not a physical alarm or calibrated ADC span. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
+          <t>Live controller magnitude was 219.494..219.924 across 15 coherent completed RUN frames. The 219..221 desired band is a provisional same-setup trend envelope, not a physical alarm or calibrated ADC span. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="AA45" s="15" t="inlineStr">
         <is>
-          <t>The 15 live frames imply atan2(Q,I)=175.022..175.032 degrees under the stated formula. Publish only after the legacy I/Q sign and phase convention is validated; the numeric band is diagnostic and no alarm is requested. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
+          <t>The 15 live frames imply atan2(Q,I)=175.022..175.032 degrees under the stated formula. Publish only after the legacy I/Q sign and phase convention is validated; the numeric band is diagnostic and no alarm is requested. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="AA47" s="13" t="inlineStr">
         <is>
-          <t>Live controller I was -219.095..-218.669 across 15 coherent completed RUN frames. The desired band is a provisional same-setup trend envelope only. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
+          <t>Live controller I was -219.095..-218.669 across 15 coherent completed RUN frames. The desired band is a provisional same-setup trend envelope only. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="AA48" s="13" t="inlineStr">
         <is>
-          <t>Live controller Q was 19.007..19.083 across 15 coherent completed RUN frames. The desired band is a provisional same-setup trend envelope only. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
+          <t>Live controller Q was 19.007..19.083 across 15 coherent completed RUN frames. The desired band is a provisional same-setup trend envelope only. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>Legacy OPC UA Server</t>
+          <t>Legacy OPC UA</t>
         </is>
       </c>
       <c r="B57" s="15" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Version of the legacy OPC UA server.</t>
+          <t>Version of the native legacy acquisition and capability-bounded OPC UA server.</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AA57" s="15" t="inlineStr">
         <is>
-          <t>The production server is under development and its initial release is read-only. The earlier off-board adapter is validation evidence; mutating capabilities below remain staged requirements.</t>
+          <t>The native target server is implemented and deployed. ThresholdOhm is its only authenticated writable variable; requested controls below remain commissioning-gated unless their Notes say implemented. On 2026-08-13 the native ARMv7 OPC UA server was deployed on the ZedBoard at TCP 4842 with target-local recovery buffering and automatic time synchronization. Anonymous sessions are read-only. An authenticated, idempotent 100-Ohm ThresholdOhm write passed persistent-file, live controller word, recovery-journal, and display-transaction readback without changing the controller or recovery process identity. Other configuration writes and all Methods remain explicitly unsupported.</t>
         </is>
       </c>
     </row>
@@ -5823,10 +5823,10 @@
         </is>
       </c>
       <c r="I60" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="14" t="n">
-        <v>500</v>
+        <v>1023</v>
       </c>
       <c r="K60" s="14" t="n">
         <v>100</v>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="AA60" s="13" t="inlineStr">
         <is>
-          <t>Readback, not a second command path. The requested initial value is 100 Ohm; the controller returned exactly 100 Ohm in every 2026-08-12 direct frame and every 2026-08-13 adapter pilot cycle. Refresh this value from the controller/display after a write.</t>
+          <t>Readback, not a second command path. The requested initial value is 100 Ohm. Refresh it from the controller journal after a write and compare Configuration.LastCommandResult. On 2026-08-13 the native ARMv7 OPC UA server was deployed on the ZedBoard at TCP 4842 with target-local recovery buffering and automatic time synchronization. Anonymous sessions are read-only. An authenticated, idempotent 100-Ohm ThresholdOhm write passed persistent-file, live controller word, recovery-journal, and display-transaction readback without changing the controller or recovery process identity. Other configuration writes and all Methods remain explicitly unsupported.</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>Model-1.3 compatibility result for the most recent accepted or rejected write/method.</t>
+          <t>Result of the most recent accepted or rejected canonical write.</t>
         </is>
       </c>
       <c r="D63" s="14" t="inlineStr">
@@ -6123,34 +6123,34 @@
       </c>
       <c r="AA63" s="13" t="inlineStr">
         <is>
-          <t>Keep for compatibility; model-1.4 Operations command-status nodes are the complete audit/readback contract.</t>
+          <t>IMPLEMENTED for the native threshold transaction and rejection reason. The model-1.4 Operations command-status nodes remain requested future audit/readback additions.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>NtpSynchronized</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Aggregate endpoint health: OK, Degraded, Failed, or Starting.</t>
+          <t>True only while current-boot target SNTP evidence remains within the 15-minute holdover bound.</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Overall</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Time.NtpSynchronized</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -6200,32 +6200,36 @@
       <c r="Z64" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA64" s="13" t="inlineStr"/>
+      <c r="AA64" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED AND LIVE. The ZedBoard queries the Fermilab-synchronized controls workstation from its secondary maintenance address. No routine manual clock setting is required.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>LastUpdate</t>
+          <t>NtpServiceActive</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Time aggregate health was last evaluated.</t>
+          <t>True when the legacy target gizmo-time-sync service process is alive.</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.LastUpdate</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Time.NtpServiceActive</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
@@ -6267,33 +6271,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y65" s="15" t="n">
-        <v>1000</v>
+      <c r="Y65" s="15" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
       </c>
       <c r="Z65" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="AA65" s="15" t="inlineStr"/>
+      <c r="AA65" s="15" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED AND LIVE. Evaluate together with NtpSynchronized; service activity alone is not proof of accurate time.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>NtpService</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of the measurement subtree.</t>
+          <t>Bounded identification of the legacy SNTP client and workstation source.</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Measurement</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Time.NtpService</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -6346,9 +6356,13 @@
         </is>
       </c>
       <c r="Z66" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA66" s="13" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="AA66" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED AND LIVE. Expected source is target SNTP via the Fermilab-synchronized controls workstation.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
@@ -6358,17 +6372,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Thermal</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of the thermal subtree.</t>
+          <t>Aggregate endpoint health: OK, Degraded, Failed, or Starting.</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Thermal</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Overall</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -6423,11 +6437,7 @@
       <c r="Z67" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA67" s="13" t="inlineStr">
-        <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
-        </is>
-      </c>
+      <c r="AA67" s="13" t="inlineStr"/>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
@@ -6437,22 +6447,22 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>LastUpdate</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of timekeeping.</t>
+          <t>Time aggregate health was last evaluated.</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Time</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.LastUpdate</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -6494,19 +6504,13 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y68" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y68" s="14" t="n">
+        <v>1000</v>
       </c>
       <c r="Z68" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA68" s="13" t="inlineStr">
-        <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
-        </is>
-      </c>
+      <c r="AA68" s="13" t="inlineStr"/>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
@@ -6516,17 +6520,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>OperatingSystem</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Aggregate quality of operating-system telemetry.</t>
+          <t>Aggregate quality of the measurement subtree.</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.OperatingSystem</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Measurement</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
@@ -6579,13 +6583,9 @@
         </is>
       </c>
       <c r="Z69" s="15" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AA69" s="15" t="inlineStr">
-        <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="AA69" s="15" t="inlineStr"/>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
@@ -6595,17 +6595,17 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Thermal</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of network monitoring.</t>
+          <t>Aggregate quality of the thermal subtree.</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Network</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Thermal</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -6658,11 +6658,11 @@
         </is>
       </c>
       <c r="Z70" s="14" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="AA70" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the native target endpoint and validated recovery record; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of storage monitoring.</t>
+          <t>Aggregate quality of timekeeping.</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Storage</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Time</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -6737,11 +6737,11 @@
         </is>
       </c>
       <c r="Z71" s="14" t="n">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="AA71" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the native target endpoint and validated recovery record; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6753,17 +6753,17 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Firmware</t>
+          <t>OperatingSystem</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of runtime and programmable-logic state.</t>
+          <t>Aggregate quality of operating-system telemetry.</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Firmware</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.OperatingSystem</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -6816,11 +6816,11 @@
         </is>
       </c>
       <c r="Z72" s="14" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="AA72" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the native target endpoint and validated recovery record; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6832,17 +6832,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Aggregate quality of owned legacy OPC UA server processes.</t>
+          <t>Aggregate quality of network monitoring.</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Services</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Network</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AA73" s="15" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the native target endpoint and validated recovery record; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6911,17 +6911,17 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of calibration metadata.</t>
+          <t>Aggregate quality of storage monitoring.</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Calibration</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Storage</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AA74" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Quality refers to the native target endpoint and validated recovery record; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
         </is>
       </c>
     </row>
@@ -6990,17 +6990,17 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>SDR</t>
+          <t>Firmware</t>
         </is>
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of SDR acquisition.</t>
+          <t>Aggregate quality of runtime and programmable-logic state.</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.SDR</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Firmware</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
@@ -7053,100 +7053,250 @@
         </is>
       </c>
       <c r="Z75" s="14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA75" s="13" t="inlineStr">
+        <is>
+          <t>Quality refers to the native target endpoint and validated recovery record; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of owned services or adapter processes.</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Services</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="n"/>
+      <c r="J76" s="14" t="n"/>
+      <c r="K76" s="14" t="n"/>
+      <c r="L76" s="14" t="n"/>
+      <c r="M76" s="14" t="n"/>
+      <c r="N76" s="14" t="n"/>
+      <c r="O76" s="14" t="n"/>
+      <c r="P76" s="14" t="n"/>
+      <c r="Q76" s="14" t="n"/>
+      <c r="R76" s="14" t="n"/>
+      <c r="S76" s="14" t="n"/>
+      <c r="T76" s="14" t="n"/>
+      <c r="U76" s="14" t="n"/>
+      <c r="V76" s="14" t="n"/>
+      <c r="W76" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X76" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y76" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z76" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AA76" s="13" t="inlineStr">
+        <is>
+          <t>Quality refers to the native target endpoint and validated recovery record; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Aggregate quality of calibration metadata.</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Calibration</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I77" s="15" t="n"/>
+      <c r="J77" s="15" t="n"/>
+      <c r="K77" s="15" t="n"/>
+      <c r="L77" s="15" t="n"/>
+      <c r="M77" s="15" t="n"/>
+      <c r="N77" s="15" t="n"/>
+      <c r="O77" s="15" t="n"/>
+      <c r="P77" s="15" t="n"/>
+      <c r="Q77" s="15" t="n"/>
+      <c r="R77" s="15" t="n"/>
+      <c r="S77" s="15" t="n"/>
+      <c r="T77" s="15" t="n"/>
+      <c r="U77" s="15" t="n"/>
+      <c r="V77" s="15" t="n"/>
+      <c r="W77" s="15" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X77" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y77" s="15" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z77" s="15" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA77" s="15" t="inlineStr">
+        <is>
+          <t>Quality refers to the native target endpoint and validated recovery record; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>SDR</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of SDR acquisition.</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.SDR</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="n"/>
+      <c r="J78" s="14" t="n"/>
+      <c r="K78" s="14" t="n"/>
+      <c r="L78" s="14" t="n"/>
+      <c r="M78" s="14" t="n"/>
+      <c r="N78" s="14" t="n"/>
+      <c r="O78" s="14" t="n"/>
+      <c r="P78" s="14" t="n"/>
+      <c r="Q78" s="14" t="n"/>
+      <c r="R78" s="14" t="n"/>
+      <c r="S78" s="14" t="n"/>
+      <c r="T78" s="14" t="n"/>
+      <c r="U78" s="14" t="n"/>
+      <c r="V78" s="14" t="n"/>
+      <c r="W78" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X78" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y78" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z78" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA75" s="13" t="inlineStr">
-        <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="n"/>
-      <c r="B76" s="11" t="n"/>
-      <c r="C76" s="11" t="n"/>
-      <c r="D76" s="11" t="n"/>
-      <c r="E76" s="11" t="n"/>
-      <c r="F76" s="11" t="n"/>
-      <c r="G76" s="11" t="n"/>
-      <c r="H76" s="11" t="n"/>
-      <c r="I76" s="11" t="n"/>
-      <c r="J76" s="11" t="n"/>
-      <c r="K76" s="11" t="n"/>
-      <c r="L76" s="11" t="n"/>
-      <c r="M76" s="11" t="n"/>
-      <c r="N76" s="11" t="n"/>
-      <c r="O76" s="11" t="n"/>
-      <c r="P76" s="11" t="n"/>
-      <c r="Q76" s="11" t="n"/>
-      <c r="R76" s="11" t="n"/>
-      <c r="S76" s="11" t="n"/>
-      <c r="T76" s="11" t="n"/>
-      <c r="U76" s="11" t="n"/>
-      <c r="V76" s="11" t="n"/>
-      <c r="W76" s="11" t="n"/>
-      <c r="X76" s="11" t="n"/>
-      <c r="Y76" s="11" t="n"/>
-      <c r="Z76" s="11" t="n"/>
-      <c r="AA76" s="11" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="n"/>
-      <c r="B77" s="11" t="n"/>
-      <c r="C77" s="11" t="n"/>
-      <c r="D77" s="11" t="n"/>
-      <c r="E77" s="11" t="n"/>
-      <c r="F77" s="11" t="n"/>
-      <c r="G77" s="11" t="n"/>
-      <c r="H77" s="11" t="n"/>
-      <c r="I77" s="11" t="n"/>
-      <c r="J77" s="11" t="n"/>
-      <c r="K77" s="11" t="n"/>
-      <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n"/>
-      <c r="O77" s="11" t="n"/>
-      <c r="P77" s="11" t="n"/>
-      <c r="Q77" s="11" t="n"/>
-      <c r="R77" s="11" t="n"/>
-      <c r="S77" s="11" t="n"/>
-      <c r="T77" s="11" t="n"/>
-      <c r="U77" s="11" t="n"/>
-      <c r="V77" s="11" t="n"/>
-      <c r="W77" s="11" t="n"/>
-      <c r="X77" s="11" t="n"/>
-      <c r="Y77" s="11" t="n"/>
-      <c r="Z77" s="11" t="n"/>
-      <c r="AA77" s="11" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="n"/>
-      <c r="B78" s="11" t="n"/>
-      <c r="C78" s="11" t="n"/>
-      <c r="D78" s="11" t="n"/>
-      <c r="E78" s="11" t="n"/>
-      <c r="F78" s="11" t="n"/>
-      <c r="G78" s="11" t="n"/>
-      <c r="H78" s="11" t="n"/>
-      <c r="I78" s="11" t="n"/>
-      <c r="J78" s="11" t="n"/>
-      <c r="K78" s="11" t="n"/>
-      <c r="L78" s="11" t="n"/>
-      <c r="M78" s="11" t="n"/>
-      <c r="N78" s="11" t="n"/>
-      <c r="O78" s="11" t="n"/>
-      <c r="P78" s="11" t="n"/>
-      <c r="Q78" s="11" t="n"/>
-      <c r="R78" s="11" t="n"/>
-      <c r="S78" s="11" t="n"/>
-      <c r="T78" s="11" t="n"/>
-      <c r="U78" s="11" t="n"/>
-      <c r="V78" s="11" t="n"/>
-      <c r="W78" s="11" t="n"/>
-      <c r="X78" s="11" t="n"/>
-      <c r="Y78" s="11" t="n"/>
-      <c r="Z78" s="11" t="n"/>
-      <c r="AA78" s="11" t="n"/>
+      <c r="AA78" s="13" t="inlineStr">
+        <is>
+          <t>Quality refers to the native target endpoint and validated recovery record; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n"/>
@@ -10803,7 +10953,7 @@
       <c r="AA204" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA75"/>
+  <autoFilter ref="A1:AA78"/>
   <dataValidations count="5">
     <dataValidation sqref="E2:E204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
       <formula1>"Boolean,Byte,Short,Integer,Long,Float,Double,String,DateTime"</formula1>
@@ -10825,7 +10975,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;BLegacy GIZMo — ZedBoard implementation</oddHeader>
-    <oddFooter>&amp;LDraft 0.7 — GIZMo OPC UA-to-Ignition requirements&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDraft 0.9 — GIZMo OPC UA-to-Ignition requirements&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/deliverables/GIZMo_ZedBoard_DCS_Intake.xlsx
+++ b/deliverables/GIZMo_ZedBoard_DCS_Intake.xlsx
@@ -10,9 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tag List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tag List'!$A$1:$AA$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tag List'!$A$1:$AA$88</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tag List'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Tag List'!$A$1:$AA$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Tag List'!$A$1:$AA$88</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -590,7 +590,7 @@
       </c>
       <c r="C1" s="17" t="inlineStr">
         <is>
-          <t>Legacy GIZMo — ZedBoard implementation</t>
+          <t>Legacy GIZMo — ZedBoard implementation under development</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>opc.tcp://&lt;assigned-host&gt;:4840 (final host/IP assigned by Slow Controls)</t>
+          <t>opc.tcp://&lt;assigned-legacy-host&gt;:4842 (commissioning target; not a deployed endpoint)</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Stable string NodeIds; resolve namespace URI at connection time; do not hard-code namespace index.</t>
+          <t>This ICD defines the authoritative, hardware-neutral urn:fnal:gizmo contract. Any GIZMo hardware implementation must conform to its stable string NodeIds, node classes, datatypes, ranks, units, meanings, quality/timestamp rules, and method signatures. Resolve the namespace URI at connection time; do not hard-code its namespace index.</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Control rows are listed first and color-coded. Green Read-Write rows are bounded configuration setpoints; amber Write-Only rows are typed OPC UA Methods. Read-Only measurement/status rows are device readbacks and must not be writable. Notes identify implemented versus commissioning-gated capabilities.</t>
+          <t>DCS Access records the effective ZedBoard integration profile, which is monitoring-only until separately accepted. Canonical methods remain listed for schema conformance but must return BadNotSupported while disabled. Notes distinguish contract requirements, recovered private hardware capability, development status, and commissioning gates.</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Draft 0.8 requirements intake for joint GIZMo / Slow Controls review</t>
+          <t>Draft 0.10 requirements intake for joint GIZMo / Slow Controls review</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Kria values use the retained 2026-07-27..2026-08-03 permanent SQLite replica as observational evidence. Legacy values use 15 direct coherent frames from the connected ZedBoard on 2026-08-12 plus 27 contiguous validation-adapter cycles on 2026-08-13; target communication was lost before the 100-cycle acceptance run completed. These sources refine nominal/desired fields but do not replace approved alarm or metrology limits.</t>
+          <t>Kria values use the retained 2026-07-27..2026-08-03 SQLite replica as observational evidence. Legacy values use 15 direct coherent frames from 2026-08-12 and 27 contiguous off-board adapter-pilot cycles from 2026-08-13. No target-native ZedBoard OPC UA deployment or authenticated write is accepted as evidence in this revision. These sources refine nominal/desired fields but do not replace approved alarm or metrology limits.</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Engineering units ONLY (degC, V, A, psia, bar...). Do NOT put units in the value columns.</t>
+          <t>EngineeringUnits value from the OPC UA contract (for example Cel, V, A, psia, bar). Do not put units in numeric value columns.</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>Validated writable legacy alarm threshold.</t>
+          <t>Canonical UInt32 alarm-threshold configuration node; effective ZedBoard access is read-only until separately accepted.</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I2" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="19" t="n">
-        <v>500</v>
+        <v>1023</v>
       </c>
       <c r="K2" s="19" t="n">
         <v>100</v>
@@ -1314,7 +1314,7 @@
       <c r="V2" s="19" t="n"/>
       <c r="W2" s="20" t="inlineStr">
         <is>
-          <t>Read-Write</t>
+          <t>Read-Only</t>
         </is>
       </c>
       <c r="X2" s="19" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AA2" s="21" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL, COMMISSIONING STAGE 2; the initial pilot shall reject writes until released. OPC UA UInt32, restricted by documented legacy policy to integer 1..500 Ohm. Requested initial/normal setpoint is 100 Ohm, matching the connected controller. Map only to allow-listed set_th N, serialize access, read back the controller/display value, audit, and fault-lock on mismatch.</t>
+          <t>CONTRACT MODEL 1.3.1; INITIAL ZEDBOARD PROFILE MONITORING-ONLY. The common UInt32 range is 0..1023 Ohm, matching the recovered controller field. No ZedBoard OPC UA threshold write is accepted by this ICD revision. Before it can be enabled, the implementation must pass authorization, serialization, non-interference, persistent/live/display readback, rollback, audit, and commissioning tests.</t>
         </is>
       </c>
     </row>
@@ -1344,17 +1344,17 @@
       </c>
       <c r="B3" s="18" t="inlineStr">
         <is>
-          <t>MeasurementPeriodSeconds</t>
+          <t>AveragesPerCalculation</t>
         </is>
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>Delay requested between normal legacy RUN measurements.</t>
+          <t>Canonical averaging-count configuration node; fixed/read-only on the ZedBoard initial profile.</t>
         </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Configuration.MeasurementPeriodSeconds</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Configuration.AveragesPerCalculation</t>
         </is>
       </c>
       <c r="E3" s="19" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
@@ -1380,15 +1380,17 @@
       <c r="I3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="19" t="n"/>
+      <c r="J3" s="19" t="n">
+        <v>1000000</v>
+      </c>
       <c r="K3" s="19" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="N3" s="19" t="n"/>
       <c r="O3" s="19" t="n"/>
@@ -1401,7 +1403,7 @@
       <c r="V3" s="19" t="n"/>
       <c r="W3" s="20" t="inlineStr">
         <is>
-          <t>Read-Write</t>
+          <t>Read-Only</t>
         </is>
       </c>
       <c r="X3" s="19" t="inlineStr">
@@ -1419,7 +1421,7 @@
       </c>
       <c r="AA3" s="21" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL, COMMISSIONING STAGE 1; the initial pilot shall reject writes until released. OPC UA UInt32. The live SysV service starts GIZMO.elf with argument 3 and the engineering note documents RUN default 3 seconds. Keep the initial value fixed at 3 until an upper bound and alternate cadences are commissioned.</t>
+          <t>Canonical UInt32 contract range is 1..1,000,000. The recovered controller uses a fixed 15 RUN accumulations, so the initial ZedBoard implementation publishes 15 and rejects writes with BadNotSupported. The RUN sleep argument is cadence, not averaging, and is not a canonical configuration node.</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1433,17 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>RestartMeasurementEngine</t>
+          <t>ClearLatch</t>
         </is>
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
-          <t>Method: restart only GIZMO.elf and resume configured normal RUN mode.</t>
+          <t>Method: clear the persistent alarm latch.</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.RestartMeasurementEngine</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.ClearLatch</t>
         </is>
       </c>
       <c r="E4" s="23" t="inlineStr">
@@ -1492,7 +1494,7 @@
       <c r="Z4" s="23" t="n"/>
       <c r="AA4" s="25" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL, COMMISSIONING STAGE 1, MAINTENANCE-ONLY. OPC UA Method: no input; String acceptance result. Broker shall verify exact executable identity, serialize ownership, enforce timeout, and confirm new PID/hash/fresh measurement sequence. This is not a board reboot.</t>
+          <t>CONTRACT MODEL 1.3.1 METHOD; DISABLED IN THE INITIAL ZEDBOARD PROFILE. Calls shall return BadNotSupported. The recovered controller has no equivalent persistent-latch operation.</t>
         </is>
       </c>
     </row>
@@ -1504,22 +1506,22 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>CaptureAdc</t>
+          <t>StartCalibration</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t>Method: request one bounded legacy ADC diagnostic capture and restore normal RUN mode.</t>
+          <t>Method: acquire a legacy relay-resistor characterization sweep with requested reads per point.</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.CaptureAdc</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.StartCalibration</t>
         </is>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="F5" s="26" t="inlineStr">
@@ -1565,7 +1567,7 @@
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="26" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL, COMMISSIONING STAGE 3, MAINTENANCE-ONLY. OPC UA Method: no input; String acceptance result. Map only to reviewed read_adc behavior; bound file size/transfer/time and verify restoration of normal acquisition.</t>
+          <t>CONTRACT MODEL 1.3.1 METHOD; DISABLED IN THE INITIAL ZEDBOARD PROFILE. Calls shall return BadNotSupported. Legacy CAL is characterization-only and lacks validated cleanup/activation semantics.</t>
         </is>
       </c>
     </row>
@@ -1577,22 +1579,22 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>SetSystemTime</t>
+          <t>CaptureAdc</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Method: set the legacy target clock using an absolute DateTime.</t>
+          <t>Method: request one bounded legacy ADC diagnostic capture and restore normal RUN mode.</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.SetSystemTime</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.CaptureAdc</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -1638,7 +1640,7 @@
       <c r="Z6" s="23" t="n"/>
       <c r="AA6" s="25" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL, COMMISSIONING STAGE 3, MAINTENANCE-ONLY. OPC UA Method: absolute DateTime input; String acceptance result. Map only to reviewed set_time behavior; verify Time.CurrentUtc/Quality and log the clock step.</t>
+          <t>CONTRACT MODEL 1.3.1 METHOD; DISABLED IN THE INITIAL ZEDBOARD PROFILE. Calls shall return BadNotSupported. A future mapping may use reviewed read_adc behavior after bounded transfer and restoration tests.</t>
         </is>
       </c>
     </row>
@@ -1650,17 +1652,17 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>StartCalibration</t>
+          <t>NormalizeMagnitude</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>Method: acquire a legacy relay-resistor characterization sweep with requested reads per point.</t>
+          <t>Method: request one-shot magnitude normalization.</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.StartCalibration</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.NormalizeMagnitude</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -1711,7 +1713,7 @@
       <c r="Z7" s="23" t="n"/>
       <c r="AA7" s="25" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL, COMMISSIONING STAGE 4, MAINTENANCE-ONLY. OPC UA Method: UInt32 reads_per_point input with approved bound; String acceptance result. Disabled until an isolated fixture, exclusive relay ownership, measured resistor provenance, progress/result readback, abort, and verified high-impedance restoration pass. Output is CharacterizationOnly and shall never auto-activate a curve.</t>
+          <t>CONTRACT MODEL 1.3.1 METHOD; DISABLED IN THE INITIAL ZEDBOARD PROFILE. Calls shall return BadNotSupported. No validated ZedBoard equivalent exists.</t>
         </is>
       </c>
     </row>
@@ -1723,22 +1725,22 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>AbortCalibration</t>
+          <t>SetSystemTime</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Method: abort an active legacy calibration and begin restoration of normal RUN/high-impedance state.</t>
+          <t>Method: set the legacy target clock using an absolute DateTime.</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.AbortCalibration</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.SetSystemTime</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -1784,7 +1786,7 @@
       <c r="Z8" s="23" t="n"/>
       <c r="AA8" s="25" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL BEFORE STAGE 4 RELEASE, MAINTENANCE-ONLY. OPC UA Method: no input; String acceptance result. Broker orchestration must be idempotent and must expose terminal failure if physical restoration cannot be verified.</t>
+          <t>CONTRACT MODEL 1.3.1 METHOD; DISABLED IN THE INITIAL ZEDBOARD PROFILE. Calls shall return BadNotSupported. Normal time synchronization and any maintenance fallback remain to be verified.</t>
         </is>
       </c>
     </row>
@@ -1796,17 +1798,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>RestoreNormalState</t>
+          <t>RestartMeasurementEngine</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>Method: command and verify the legacy normal RUN/high-impedance calibration state.</t>
+          <t>Method: restart only GIZMO.elf and resume configured normal RUN mode.</t>
         </is>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.RestoreNormalState</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.RestartMeasurementEngine</t>
         </is>
       </c>
       <c r="E9" s="26" t="inlineStr">
@@ -1857,165 +1859,153 @@
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="26" t="inlineStr">
         <is>
-          <t>REQUIRED CONTROL BEFORE STAGE 4 RELEASE, MAINTENANCE-ONLY RECOVERY. OPC UA Method: no input; String acceptance result. Use the reviewed high-Z sequence through the exclusive broker; never expose set_res, set_rly, relay bits, or MMIO as DCS controls.</t>
+          <t>REQUIRED MODEL 1.4 PROPOSAL; NOT PART OF MODEL 1.3.1 AND DISABLED. It shall not be advertised under model 1.3.1. A future implementation must name this narrow scope and prove serialized ownership and recovery.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Operation Status</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>CommandGateState</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Mutating-command gate state: Disabled, Ready, Busy, MaintenanceLocked, or FaultLocked.</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.CommandGateState</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>AbortCalibration</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Method: abort an active legacy calibration and begin restoration of normal RUN/high-impedance state.</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.AbortCalibration</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I10" s="14" t="n"/>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="14" t="n"/>
-      <c r="N10" s="14" t="n"/>
-      <c r="O10" s="14" t="n"/>
-      <c r="P10" s="14" t="n"/>
-      <c r="Q10" s="14" t="n"/>
-      <c r="R10" s="14" t="n"/>
-      <c r="S10" s="14" t="n"/>
-      <c r="T10" s="14" t="n"/>
-      <c r="U10" s="14" t="n"/>
-      <c r="V10" s="14" t="n"/>
-      <c r="W10" s="14" t="inlineStr">
-        <is>
-          <t>Read-Only</t>
-        </is>
-      </c>
-      <c r="X10" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y10" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
-      </c>
-      <c r="Z10" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" s="13" t="inlineStr">
-        <is>
-          <t>REQUIRED MODEL 1.4 READBACK. Ignition shall disable command widgets unless this state and the authenticated role permit the requested action.</t>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="23" t="n"/>
+      <c r="L10" s="23" t="n"/>
+      <c r="M10" s="23" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="23" t="n"/>
+      <c r="P10" s="23" t="n"/>
+      <c r="Q10" s="23" t="n"/>
+      <c r="R10" s="23" t="n"/>
+      <c r="S10" s="23" t="n"/>
+      <c r="T10" s="23" t="n"/>
+      <c r="U10" s="23" t="n"/>
+      <c r="V10" s="23" t="n"/>
+      <c r="W10" s="24" t="inlineStr">
+        <is>
+          <t>Write-Only</t>
+        </is>
+      </c>
+      <c r="X10" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y10" s="23" t="n"/>
+      <c r="Z10" s="23" t="n"/>
+      <c r="AA10" s="25" t="inlineStr">
+        <is>
+          <t>REQUIRED MODEL 1.4 PROPOSAL; NOT PART OF MODEL 1.3.1 AND DISABLED. It shall not be advertised under model 1.3.1. Required before any future calibration method could be enabled.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Operation Status</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>LastCommandId</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Opaque identifier assigned to the most recent accepted or rejected mutating request.</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandId</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>RestoreNormalState</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Method: command and verify the legacy normal RUN/high-impedance calibration state.</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.RestoreNormalState</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I11" s="14" t="n"/>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="14" t="n"/>
-      <c r="N11" s="14" t="n"/>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="14" t="n"/>
-      <c r="Q11" s="14" t="n"/>
-      <c r="R11" s="14" t="n"/>
-      <c r="S11" s="14" t="n"/>
-      <c r="T11" s="14" t="n"/>
-      <c r="U11" s="14" t="n"/>
-      <c r="V11" s="14" t="n"/>
-      <c r="W11" s="14" t="inlineStr">
-        <is>
-          <t>Read-Only</t>
-        </is>
-      </c>
-      <c r="X11" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y11" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
-      </c>
-      <c r="Z11" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" s="13" t="inlineStr">
-        <is>
-          <t>REQUIRED MODEL 1.4 READBACK. Correlates the operator request, device execution, and Ignition audit/history event.</t>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="23" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+      <c r="R11" s="23" t="n"/>
+      <c r="S11" s="23" t="n"/>
+      <c r="T11" s="23" t="n"/>
+      <c r="U11" s="23" t="n"/>
+      <c r="V11" s="23" t="n"/>
+      <c r="W11" s="24" t="inlineStr">
+        <is>
+          <t>Write-Only</t>
+        </is>
+      </c>
+      <c r="X11" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y11" s="23" t="n"/>
+      <c r="Z11" s="23" t="n"/>
+      <c r="AA11" s="25" t="inlineStr">
+        <is>
+          <t>REQUIRED MODEL 1.4 PROPOSAL; NOT PART OF MODEL 1.3.1 AND DISABLED. It shall not be advertised under model 1.3.1. Required before any future calibration method could be enabled; raw relay/MMIO is never exposed.</t>
         </is>
       </c>
     </row>
@@ -2027,17 +2017,17 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>LastCommandName</t>
+          <t>CommandGateState</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Canonical name of the most recent accepted or rejected mutating request.</t>
+          <t>Mutating-command gate state: Disabled, Ready, Busy, MaintenanceLocked, or FaultLocked.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandName</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.CommandGateState</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -2094,7 +2084,7 @@
       </c>
       <c r="AA12" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 READBACK. Includes configuration writes as well as Method calls.</t>
+          <t>REQUIRED MODEL 1.4 READBACK. Ignition shall disable command widgets unless this state and the authenticated role permit the requested action.</t>
         </is>
       </c>
     </row>
@@ -2106,17 +2096,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>LastCommandParameters</t>
+          <t>LastCommandId</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Bounded, sanitized parameter summary for the most recent mutating request.</t>
+          <t>Opaque identifier assigned to the most recent accepted or rejected mutating request.</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandParameters</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandId</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -2173,7 +2163,7 @@
       </c>
       <c r="AA13" s="15" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 AUDIT READBACK. Secrets and arbitrary command text are prohibited.</t>
+          <t>REQUIRED MODEL 1.4 READBACK. Correlates the operator request, device execution, and Ignition audit/history event.</t>
         </is>
       </c>
     </row>
@@ -2185,17 +2175,17 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>LastCommandRequester</t>
+          <t>LastCommandName</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Authenticated user/service identity associated with the most recent mutating request.</t>
+          <t>Canonical name of the most recent accepted or rejected mutating request.</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandRequester</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandName</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -2252,7 +2242,7 @@
       </c>
       <c r="AA14" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 AUDIT READBACK. Anonymous production writes are prohibited.</t>
+          <t>REQUIRED MODEL 1.4 READBACK. Includes configuration writes as well as Method calls.</t>
         </is>
       </c>
     </row>
@@ -2264,17 +2254,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>LastCommandState</t>
+          <t>LastCommandParameters</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Execution state: Idle, Accepted, Running, Succeeded, Failed, Rejected, or TimedOut.</t>
+          <t>Bounded, sanitized parameter summary for the most recent mutating request.</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandState</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandParameters</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -2331,7 +2321,7 @@
       </c>
       <c r="AA15" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 READBACK. SC shall not infer physical success from method return alone.</t>
+          <t>REQUIRED MODEL 1.4 AUDIT READBACK. Secrets and arbitrary command text are prohibited.</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2333,22 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>LastCommandRequestTime</t>
+          <t>LastCommandRequester</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>UTC source time at which the most recent mutating request was received.</t>
+          <t>Authenticated user/service identity associated with the most recent mutating request.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandRequestTime</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandRequester</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -2410,7 +2400,7 @@
       </c>
       <c r="AA16" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 READBACK.</t>
+          <t>REQUIRED MODEL 1.4 AUDIT READBACK. Anonymous production writes are prohibited.</t>
         </is>
       </c>
     </row>
@@ -2422,22 +2412,22 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>LastCommandCompletionTime</t>
+          <t>LastCommandState</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>UTC source time at which the most recent mutating request reached a terminal state.</t>
+          <t>Execution state: Idle, Accepted, Running, Succeeded, Failed, Rejected, or TimedOut.</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandCompletionTime</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandState</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -2489,7 +2479,7 @@
       </c>
       <c r="AA17" s="15" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 READBACK. Non-good while a command is active or before any command has completed.</t>
+          <t>REQUIRED MODEL 1.4 READBACK. SC shall not infer physical success from method return alone.</t>
         </is>
       </c>
     </row>
@@ -2501,22 +2491,22 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>LastCommandResult</t>
+          <t>LastCommandRequestTime</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Bounded result or failure reason for the most recent mutating request.</t>
+          <t>UTC source time at which the most recent mutating request was received.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandResult</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandRequestTime</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2568,34 +2558,34 @@
       </c>
       <c r="AA18" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 READBACK. Configuration.LastCommandResult remains as the model-1.3 compatibility value.</t>
+          <t>REQUIRED MODEL 1.4 READBACK.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Operation Status</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>OperationState</t>
+          <t>LastCommandCompletionTime</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Calibration execution state: Idle, Starting, Running, Restoring, Completed, Failed, Aborted, or Unknown.</t>
+          <t>UTC source time at which the most recent mutating request reached a terminal state.</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.OperationState</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandCompletionTime</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -2647,39 +2637,39 @@
       </c>
       <c r="AA19" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 READBACK before StartCalibration is enabled for routine SC use.</t>
+          <t>REQUIRED MODEL 1.4 READBACK. Non-good while a command is active or before any command has completed.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Operation Status</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>ProgressPercent</t>
+          <t>LastCommandResult</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Best available completion estimate for the active calibration operation.</t>
+          <t>Bounded result or failure reason for the most recent mutating request.</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.ProgressPercent</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Operations.LastCommandResult</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -2692,12 +2682,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>100</v>
-      </c>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
       <c r="K20" s="14" t="n"/>
       <c r="L20" s="14" t="n"/>
       <c r="M20" s="14" t="n"/>
@@ -2720,15 +2706,17 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y20" s="14" t="n">
-        <v>1000</v>
+      <c r="Y20" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
       </c>
       <c r="Z20" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="AA20" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 READBACK. Unknown progress shall carry a non-good StatusCode, not a fabricated zero.</t>
+          <t>REQUIRED MODEL 1.4 READBACK. Configuration.LastCommandResult remains as the model-1.3 compatibility value.</t>
         </is>
       </c>
     </row>
@@ -2740,22 +2728,22 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>LastOperationTime</t>
+          <t>OperationState</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>UTC completion/failure/abort time of the most recent calibration operation.</t>
+          <t>Calibration execution state: Idle, Starting, Running, Restoring, Completed, Failed, Aborted, or Unknown.</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.LastOperationTime</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.OperationState</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -2807,7 +2795,7 @@
       </c>
       <c r="AA21" s="15" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 READBACK.</t>
+          <t>REQUIRED MODEL 1.4 READBACK before StartCalibration is enabled for routine SC use.</t>
         </is>
       </c>
     </row>
@@ -2819,27 +2807,27 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>LastOperationResult</t>
+          <t>ProgressPercent</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Bounded calibration result, validation summary, or failure reason.</t>
+          <t>Best available completion estimate for the active calibration operation.</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.LastOperationResult</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.ProgressPercent</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2852,8 +2840,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I22" s="14" t="n"/>
-      <c r="J22" s="14" t="n"/>
+      <c r="I22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="K22" s="14" t="n"/>
       <c r="L22" s="14" t="n"/>
       <c r="M22" s="14" t="n"/>
@@ -2876,17 +2868,15 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y22" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y22" s="14" t="n">
+        <v>1000</v>
       </c>
       <c r="Z22" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="AA22" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 READBACK. A completed sweep is not equivalent to an activated calibration.</t>
+          <t>REQUIRED MODEL 1.4 READBACK. Unknown progress shall carry a non-good StatusCode, not a fabricated zero.</t>
         </is>
       </c>
     </row>
@@ -2898,22 +2888,22 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>RestorationState</t>
+          <t>LastOperationTime</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Post-operation normal-state restoration: NotRequired, Commanded, Verified, Failed, or Unknown.</t>
+          <t>UTC completion/failure/abort time of the most recent calibration operation.</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.RestorationState</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.LastOperationTime</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -2965,29 +2955,29 @@
       </c>
       <c r="AA23" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 SAFETY READBACK. Verified requires approved evidence of the normal high-impedance measurement state; command completion alone is only Commanded.</t>
+          <t>REQUIRED MODEL 1.4 READBACK.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Manufacturer</t>
+          <t>LastOperationResult</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Organization responsible for the GIZMo runtime package and canonical information model.</t>
+          <t>Bounded calibration result, validation summary, or failure reason.</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.Manufacturer</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.LastOperationResult</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -3031,38 +3021,42 @@
       </c>
       <c r="X24" s="14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y24" s="14" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y24" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
       <c r="Z24" s="14" t="n">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="AA24" s="13" t="inlineStr">
         <is>
-          <t>IMPLEMENTED MODEL 1.3. Published value: Fermi National Accelerator Laboratory.</t>
+          <t>REQUIRED MODEL 1.4 READBACK. A completed sweep is not equivalent to an activated calibration.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>ProductName</t>
+          <t>RestorationState</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Instrument product/platform name; expected value Legacy GIZMo (ZedBoard).</t>
+          <t>Post-operation normal-state restoration: NotRequired, Commanded, Verified, Failed, or Unknown.</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ProductName</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.RestorationState</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -3106,14 +3100,22 @@
       </c>
       <c r="X25" s="15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y25" s="15" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y25" s="15" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
       <c r="Z25" s="15" t="n">
-        <v>30000</v>
-      </c>
-      <c r="AA25" s="15" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="AA25" s="15" t="inlineStr">
+        <is>
+          <t>REQUIRED MODEL 1.4 SAFETY READBACK. Verified requires approved evidence of the normal high-impedance measurement state; command completion alone is only Commanded.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
@@ -3123,17 +3125,17 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>ModelNamespaceUri</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Canonical OPC UA namespace URI.</t>
+          <t>Organization responsible for this GIZMo implementation.</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ModelNamespaceUri</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.Manufacturer</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
@@ -3184,7 +3186,11 @@
       <c r="Z26" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="AA26" s="13" t="inlineStr"/>
+      <c r="AA26" s="13" t="inlineStr">
+        <is>
+          <t>CONTRACT MODEL 1.3.1. Published value: Fermi National Accelerator Laboratory.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
@@ -3194,17 +3200,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>ModelVersion</t>
+          <t>ProductName</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Semantic version of the canonical OPC UA information model.</t>
+          <t>Instrument product/platform name; expected value Legacy GIZMo (ZedBoard).</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ModelVersion</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ProductName</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -3255,7 +3261,7 @@
       <c r="Z27" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="AA27" s="13" t="inlineStr"/>
+      <c r="AA27" s="13" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
@@ -3265,17 +3271,17 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>RuntimeVersion</t>
+          <t>ModelNamespaceUri</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Installed legacy GIZMo OPC UA server version.</t>
+          <t>Namespace URI of the hardware-neutral GIZMo–SC OPC UA contract defined by the ICD.</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.RuntimeVersion</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ModelNamespaceUri</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
@@ -3326,7 +3332,7 @@
       <c r="Z28" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="AA28" s="13" t="inlineStr"/>
+      <c r="AA28" s="13" t="n"/>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
@@ -3336,17 +3342,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Hostname</t>
+          <t>ModelVersion</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Host running the OPC UA endpoint.</t>
+          <t>Semantic version of the hardware-neutral GIZMo–SC OPC UA contract implemented by this producer.</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.Hostname</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ModelVersion</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -3397,7 +3403,7 @@
       <c r="Z29" s="15" t="n">
         <v>30000</v>
       </c>
-      <c r="AA29" s="15" t="inlineStr"/>
+      <c r="AA29" s="15" t="n"/>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
@@ -3407,17 +3413,17 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>BootId</t>
+          <t>RuntimeVersion</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Linux boot identifier of the target or reviewed host running the legacy OPC UA server.</t>
+          <t>Version of the ZedBoard OPC UA producer under development.</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.BootId</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.RuntimeVersion</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
@@ -3461,22 +3467,14 @@
       </c>
       <c r="X30" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y30" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y30" s="14" t="n"/>
       <c r="Z30" s="14" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AA30" s="13" t="inlineStr">
-        <is>
-          <t>A target reboot, GIZMO.elf PID/hash change, or server restart opens a new Ignition history epoch; it does not change the meaning of this node.</t>
-        </is>
-      </c>
+        <v>30000</v>
+      </c>
+      <c r="AA30" s="13" t="n"/>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
@@ -3486,17 +3484,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>DeviceId</t>
+          <t>Hostname</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>Stable privacy-preserving device identifier.</t>
+          <t>Host running the OPC UA endpoint.</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.DeviceId</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.Hostname</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -3547,7 +3545,7 @@
       <c r="Z31" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="AA31" s="13" t="inlineStr"/>
+      <c r="AA31" s="13" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
@@ -3557,22 +3555,22 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>ModelPublicationDate</t>
+          <t>BootId</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Publication date of the canonical OPC UA information model.</t>
+          <t>Boot identifier for this ZedBoard instance; changes after the controller boots.</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ModelPublicationDate</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.BootId</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3611,16 +3609,20 @@
       </c>
       <c r="X32" s="14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y32" s="14" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y32" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
       <c r="Z32" s="14" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="AA32" s="13" t="inlineStr">
         <is>
-          <t>IMPLEMENTED MODEL 1.3. The published model date is 2026-07-27 UTC.</t>
+          <t>A target reboot establishes a new device-history epoch. An OPC UA server restart changes ServerStartTime but shall not change BootId or perturb GIZMO.elf.</t>
         </is>
       </c>
     </row>
@@ -3632,22 +3634,22 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>ServerStartTime</t>
+          <t>DeviceId</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Time the OPC UA server process started.</t>
+          <t>Stable privacy-preserving device identifier.</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ServerStartTime</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.DeviceId</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
@@ -3686,43 +3688,39 @@
       </c>
       <c r="X33" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y33" s="15" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y33" s="15" t="n"/>
       <c r="Z33" s="15" t="n">
         <v>30000</v>
       </c>
-      <c r="AA33" s="15" t="inlineStr"/>
+      <c r="AA33" s="15" t="n"/>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Sequence</t>
+          <t>ModelPublicationDate</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Incremented once per coherent completed GIZMO.elf RUN cycle, never once per polling attempt.</t>
+          <t>Publication date of the hardware-neutral GIZMo–SC OPC UA contract version.</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.Sequence</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ModelPublicationDate</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3761,40 +3759,38 @@
       </c>
       <c r="X34" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y34" s="14" t="n">
-        <v>1000</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y34" s="14" t="n"/>
       <c r="Z34" s="14" t="n">
-        <v>1000</v>
+        <v>30000</v>
       </c>
       <c r="AA34" s="13" t="inlineStr">
         <is>
-          <t>OPC UA built-in type UInt64. Increment only after coherent-frame validation. The 2026-08-13 deployed-adapter pilot captured contiguous Sequence 21..47 before target communication was lost.</t>
+          <t>CONTRACT MODEL 1.3.1. Published 2026-08-13 UTC.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>SampleTime</t>
+          <t>ServerStartTime</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>Legacy server receive time until target time is synchronized; status remains uncertain when substituted.</t>
+          <t>Time the OPC UA server process started.</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.SampleTime</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Identity.ServerStartTime</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
@@ -3841,13 +3837,15 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y35" s="14" t="n">
-        <v>1000</v>
+      <c r="Y35" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
       </c>
       <c r="Z35" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" s="13" t="inlineStr"/>
+        <v>30000</v>
+      </c>
+      <c r="AA35" s="13" t="n"/>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="14" t="inlineStr">
@@ -3857,27 +3855,27 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>ResistanceOhm</t>
+          <t>Sequence</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Equivalent resistive impedance at the stimulus frequency; valid only while ResistanceRange is InRange.</t>
+          <t>Incremented once per coherent completed GIZMO.elf RUN cycle, never once per polling attempt.</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.ResistanceOhm</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.Sequence</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Ohm</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3890,21 +3888,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="K36" s="14" t="n">
-        <v>112</v>
-      </c>
-      <c r="L36" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="M36" s="14" t="n">
-        <v>500</v>
-      </c>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
       <c r="N36" s="14" t="n"/>
       <c r="O36" s="14" t="n"/>
       <c r="P36" s="14" t="n"/>
@@ -3932,7 +3920,7 @@
       </c>
       <c r="AA36" s="13" t="inlineStr">
         <is>
-          <t>Documented legacy presentation range is 0..500 Ohm; values above 500 are HIGH Z. The controller's internal estimate is mathematically clamped at 999 Ohm, but 999 is not a physical span endpoint. The installed CT/inductor calibration is not yet revalidated. The current connected electronics-only setup produced 111.554..111.902 Ohm across 15 coherent completed RUN frames and the screen displayed 112 Ohm/green. Nominal 112 is therefore a dated live observation, not a detector-loop target. The requested finite normal band is 100..500 Ohm; HIGH Z is also normal. Do not configure a second independent ResistanceOhm comparison once authoritative Alarm.Active is available. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits. The deployed read-only adapter then captured 27 contiguous cycles (Sequence 21..47) on 2026-08-13: 111.465703..112.010978 Ohm, mean 111.722419 Ohm, and exactly 100 Ohm threshold; the calculated legacy display-equivalent rounding was 112 Ohm in 26 cycles and 111 Ohm in one. The samples carried UncertainLastUsableValue and Measurement.Quality=Uncertain, consistent with the unvalidated legacy measurement path. Target communication was lost before the requested 100 cycles completed, so this is additional commissioning evidence, not acceptance.</t>
+          <t>OPC UA built-in type UInt64. Increment only after coherent-frame validation. The 2026-08-13 deployed-adapter pilot captured contiguous Sequence 21..47 before target communication was lost.</t>
         </is>
       </c>
     </row>
@@ -3944,22 +3932,22 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>ResistanceRange</t>
+          <t>SampleTime</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Interpretation of ResistanceOhm: InRange, OutOfRange, Invalid, or Unknown.</t>
+          <t>Target-local recovery-record source time; quality is non-good whenever current-boot target synchronization evidence is unavailable or stale.</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.ResistanceRange</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.SampleTime</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
@@ -4001,15 +3989,13 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y37" s="15" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y37" s="15" t="n">
+        <v>1000</v>
       </c>
       <c r="Z37" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="AA37" s="15" t="inlineStr"/>
+      <c r="AA37" s="15" t="n"/>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="14" t="inlineStr">
@@ -4019,17 +4005,17 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>CapacitanceNanofarad</t>
+          <t>ResistanceOhm</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Equivalent capacitive component estimated by the active calibration.</t>
+          <t>Equivalent resistive impedance at the stimulus frequency; valid only while ResistanceRange is InRange.</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.CapacitanceNanofarad</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.ResistanceOhm</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
@@ -4039,7 +4025,7 @@
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>nF</t>
+          <t>Ohm</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -4055,10 +4041,18 @@
       <c r="I38" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="14" t="n"/>
-      <c r="K38" s="14" t="n"/>
-      <c r="L38" s="14" t="n"/>
-      <c r="M38" s="14" t="n"/>
+      <c r="J38" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="K38" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M38" s="14" t="n">
+        <v>500</v>
+      </c>
       <c r="N38" s="14" t="n"/>
       <c r="O38" s="14" t="n"/>
       <c r="P38" s="14" t="n"/>
@@ -4086,7 +4080,7 @@
       </c>
       <c r="AA38" s="13" t="inlineStr">
         <is>
-          <t>BadNotSupported/NaN in the initial legacy endpoint; the legacy self-calibration/capacitance model is not validated.</t>
+          <t>Documented legacy presentation range is 0..500 Ohm; values above 500 are HIGH Z. The controller's internal estimate is mathematically clamped at 999 Ohm, but 999 is not a physical span endpoint. The installed CT/inductor calibration is not yet revalidated. The current connected electronics-only setup produced 111.554..111.902 Ohm across 15 coherent completed RUN frames and the screen displayed 112 Ohm/green. Nominal 112 is therefore a dated live observation, not a detector-loop target. The requested finite normal band is 100..500 Ohm; HIGH Z is also normal. Do not configure a second independent ResistanceOhm comparison once authoritative Alarm.Active is available. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits. The deployed read-only adapter then captured 27 contiguous cycles (Sequence 21..47) on 2026-08-13: 111.465703..112.010978 Ohm, mean 111.722419 Ohm, and exactly 100 Ohm threshold; the calculated legacy display-equivalent rounding was 112 Ohm in 26 cycles and 111 Ohm in one. The samples carried UncertainLastUsableValue and Measurement.Quality=Uncertain, consistent with the unvalidated legacy measurement path. Target communication was lost before the requested 100 cycles completed, so this is additional commissioning evidence, not acceptance.</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4092,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>CapacitanceRange</t>
+          <t>ResistanceRange</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>Interpretation of CapacitanceNanofarad.</t>
+          <t>Interpretation of ResistanceOhm: InRange, OutOfRange, Invalid, or Unknown.</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.CapacitanceRange</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.ResistanceRange</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
@@ -4163,11 +4157,7 @@
       <c r="Z39" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA39" s="13" t="inlineStr">
-        <is>
-          <t>BadNotSupported in the initial legacy endpoint.</t>
-        </is>
-      </c>
+      <c r="AA39" s="13" t="n"/>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="14" t="inlineStr">
@@ -4177,17 +4167,17 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>ThresholdOhm</t>
+          <t>CapacitanceNanofarad</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Alarm threshold active in the measurement engine.</t>
+          <t>Equivalent capacitive component estimated by the active calibration.</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.ThresholdOhm</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.CapacitanceNanofarad</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
@@ -4197,7 +4187,7 @@
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Ohm</t>
+          <t>nF</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -4211,20 +4201,12 @@
         </is>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="K40" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="L40" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="M40" s="14" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J40" s="14" t="n"/>
+      <c r="K40" s="14" t="n"/>
+      <c r="L40" s="14" t="n"/>
+      <c r="M40" s="14" t="n"/>
       <c r="N40" s="14" t="n"/>
       <c r="O40" s="14" t="n"/>
       <c r="P40" s="14" t="n"/>
@@ -4244,17 +4226,15 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y40" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y40" s="14" t="n">
+        <v>1000</v>
       </c>
       <c r="Z40" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="AA40" s="13" t="inlineStr">
         <is>
-          <t>Live global_th readback was exactly 100 Ohm in every one of 15 coherent completed RUN frames on 2026-08-12 and every one of 27 deployed-adapter pilot cycles on 2026-08-13. Use 100 Ohm as the requested initial setpoint. The display wire field is 10 bits, but the documented legacy threshold operating range is integer 1..500 Ohm.</t>
+          <t>BadNotSupported/NaN in the initial legacy endpoint; the legacy self-calibration/capacitance model is not validated.</t>
         </is>
       </c>
     </row>
@@ -4266,27 +4246,27 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>StimulusFrequencyHertz</t>
+          <t>CapacitanceRange</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Nominal sine-wave stimulus frequency.</t>
+          <t>Interpretation of CapacitanceNanofarad.</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.StimulusFrequencyHertz</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.CapacitanceRange</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
@@ -4301,15 +4281,9 @@
       </c>
       <c r="I41" s="15" t="n"/>
       <c r="J41" s="15" t="n"/>
-      <c r="K41" s="15" t="n">
-        <v>1470.6</v>
-      </c>
-      <c r="L41" s="15" t="n">
-        <v>1470</v>
-      </c>
-      <c r="M41" s="15" t="n">
-        <v>1472</v>
-      </c>
+      <c r="K41" s="15" t="n"/>
+      <c r="L41" s="15" t="n"/>
+      <c r="M41" s="15" t="n"/>
       <c r="N41" s="15" t="n"/>
       <c r="O41" s="15" t="n"/>
       <c r="P41" s="15" t="n"/>
@@ -4339,7 +4313,7 @@
       </c>
       <c r="AA41" s="15" t="inlineStr">
         <is>
-          <t>Measured at the powered rear TO DETECTOR output with a Fluke 287 on 2026-08-11: 1470.6 Hz. The live 2026-08-12 controller readback remained frequency_multiplier=1 with waveform_length=999. Desired 1470..1472 Hz is a provisional commissioning check band, not an alarm limit.</t>
+          <t>BadNotSupported in the initial legacy endpoint.</t>
         </is>
       </c>
     </row>
@@ -4351,17 +4325,17 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>StimulusCurrentRmsAmpere</t>
+          <t>ThresholdOhm</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>RMS AC stimulus current delivered to the detector-ground measurement path.</t>
+          <t>Alarm threshold active in the measurement engine.</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.StimulusCurrentRmsAmpere</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.ThresholdOhm</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
@@ -4371,7 +4345,7 @@
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Ohm</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -4387,10 +4361,18 @@
       <c r="I42" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="14" t="n"/>
-      <c r="K42" s="14" t="n"/>
-      <c r="L42" s="14" t="n"/>
-      <c r="M42" s="14" t="n"/>
+      <c r="J42" s="14" t="n">
+        <v>1023</v>
+      </c>
+      <c r="K42" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="L42" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="N42" s="14" t="n"/>
       <c r="O42" s="14" t="n"/>
       <c r="P42" s="14" t="n"/>
@@ -4410,15 +4392,17 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y42" s="14" t="n">
-        <v>1000</v>
+      <c r="Y42" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
       </c>
       <c r="Z42" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="AA42" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MODEL 1.4 MONITOR VALUE from the Slow Controls analysis. BadNotSupported initially. The legacy amplifier has a Stimulus Current Monitor point, but its transfer function, loading, acquisition method, RMS conversion, bandwidth, and uncertainty must be validated before publishing amperes.</t>
+          <t>Read-only global_th was exactly 100 Ohm in all 15 direct coherent frames and all 27 off-board adapter-pilot cycles. Use 100 Ohm as the requested initial setpoint. The common model-1.3.1 range and recovered controller field are both 0..1023; no ZedBoard OPC UA write is accepted by this revision.</t>
         </is>
       </c>
     </row>
@@ -4430,17 +4414,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>MagnitudeCount</t>
+          <t>StimulusFrequencyHertz</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>Lock-in magnitude in uncalibrated ADC counts.</t>
+          <t>Nominal sine-wave stimulus frequency.</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.MagnitudeCount</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.StimulusFrequencyHertz</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -4450,7 +4434,7 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -4466,13 +4450,13 @@
       <c r="I43" s="14" t="n"/>
       <c r="J43" s="14" t="n"/>
       <c r="K43" s="14" t="n">
-        <v>219.76</v>
+        <v>1470.6</v>
       </c>
       <c r="L43" s="14" t="n">
-        <v>219</v>
+        <v>1470</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>221</v>
+        <v>1472</v>
       </c>
       <c r="N43" s="14" t="n"/>
       <c r="O43" s="14" t="n"/>
@@ -4493,15 +4477,17 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y43" s="14" t="n">
-        <v>1000</v>
+      <c r="Y43" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
       </c>
       <c r="Z43" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="AA43" s="13" t="inlineStr">
         <is>
-          <t>Live controller magnitude was 219.494..219.924 across 15 coherent completed RUN frames. The 219..221 desired band is a provisional same-setup trend envelope, not a physical alarm or calibrated ADC span. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
+          <t>Measured at the powered rear TO DETECTOR output with a Fluke 287 on 2026-08-11: 1470.6 Hz. The live 2026-08-12 controller readback remained frequency_multiplier=1 with waveform_length=999. Desired 1470..1472 Hz is a provisional commissioning check band, not an alarm limit.</t>
         </is>
       </c>
     </row>
@@ -4513,17 +4499,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>PhaseAtanDegrees</t>
+          <t>StimulusCurrentRmsAmpere</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Phase calculated using atan.</t>
+          <t>RMS AC stimulus current delivered to the detector-ground measurement path.</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.PhaseAtanDegrees</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.StimulusCurrentRmsAmpere</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
@@ -4533,7 +4519,7 @@
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -4547,11 +4533,9 @@
         </is>
       </c>
       <c r="I44" s="14" t="n">
-        <v>-90</v>
-      </c>
-      <c r="J44" s="14" t="n">
-        <v>90</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J44" s="14" t="n"/>
       <c r="K44" s="14" t="n"/>
       <c r="L44" s="14" t="n"/>
       <c r="M44" s="14" t="n"/>
@@ -4582,7 +4566,7 @@
       </c>
       <c r="AA44" s="13" t="inlineStr">
         <is>
-          <t>BadNotSupported initially.</t>
+          <t>REQUIRED MODEL 1.4 MONITOR VALUE from the Slow Controls analysis. BadNotSupported initially. The legacy amplifier has a Stimulus Current Monitor point, but its transfer function, loading, acquisition method, RMS conversion, bandwidth, and uncertainty must be validated before publishing amperes.</t>
         </is>
       </c>
     </row>
@@ -4594,17 +4578,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>PhaseAtan2Degrees</t>
+          <t>MagnitudeCount</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>Phase calculated using atan2.</t>
+          <t>Lock-in magnitude in uncalibrated ADC counts.</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.PhaseAtan2Degrees</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.MagnitudeCount</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
@@ -4614,7 +4598,7 @@
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G45" s="15" t="inlineStr">
@@ -4624,23 +4608,19 @@
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>degrees(atan2(Q,I)) after a sign/convention validation test</t>
-        </is>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-180</v>
-      </c>
-      <c r="J45" s="15" t="n">
-        <v>180</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="n"/>
+      <c r="J45" s="15" t="n"/>
       <c r="K45" s="15" t="n">
-        <v>175.03</v>
+        <v>219.76</v>
       </c>
       <c r="L45" s="15" t="n">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="M45" s="15" t="n">
-        <v>175.1</v>
+        <v>221</v>
       </c>
       <c r="N45" s="15" t="n"/>
       <c r="O45" s="15" t="n"/>
@@ -4669,7 +4649,7 @@
       </c>
       <c r="AA45" s="15" t="inlineStr">
         <is>
-          <t>The 15 live frames imply atan2(Q,I)=175.022..175.032 degrees under the stated formula. Publish only after the legacy I/Q sign and phase convention is validated; the numeric band is diagnostic and no alarm is requested. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
+          <t>Live controller magnitude was 219.494..219.924 across 15 coherent completed RUN frames. The 219..221 desired band is a provisional same-setup trend envelope, not a physical alarm or calibrated ADC span. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
         </is>
       </c>
     </row>
@@ -4681,17 +4661,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>PhaseInterpolatedDegrees</t>
+          <t>PhaseAtanDegrees</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Phase used by impedance calibration interpolation.</t>
+          <t>Phase calculated using atan.</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.PhaseInterpolatedDegrees</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.PhaseAtanDegrees</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
@@ -4714,8 +4694,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I46" s="14" t="n"/>
-      <c r="J46" s="14" t="n"/>
+      <c r="I46" s="14" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>90</v>
+      </c>
       <c r="K46" s="14" t="n"/>
       <c r="L46" s="14" t="n"/>
       <c r="M46" s="14" t="n"/>
@@ -4758,17 +4742,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>InPhaseCount</t>
+          <t>PhaseAtan2Degrees</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>Lock-in in-phase component in ADC counts.</t>
+          <t>Phase calculated using atan2.</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.InPhaseCount</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.PhaseAtan2Degrees</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -4778,7 +4762,7 @@
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -4788,19 +4772,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="n"/>
-      <c r="J47" s="14" t="n"/>
+          <t>degrees(atan2(Q,I)) after a sign/convention validation test</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>-180</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>180</v>
+      </c>
       <c r="K47" s="14" t="n">
-        <v>-218.931</v>
+        <v>175.03</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>-220</v>
+        <v>175</v>
       </c>
       <c r="M47" s="14" t="n">
-        <v>-218</v>
+        <v>175.1</v>
       </c>
       <c r="N47" s="14" t="n"/>
       <c r="O47" s="14" t="n"/>
@@ -4829,7 +4817,7 @@
       </c>
       <c r="AA47" s="13" t="inlineStr">
         <is>
-          <t>Live controller I was -219.095..-218.669 across 15 coherent completed RUN frames. The desired band is a provisional same-setup trend envelope only. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
+          <t>The 15 live frames imply atan2(Q,I)=175.022..175.032 degrees under the stated formula. Publish only after the legacy I/Q sign and phase convention is validated; the numeric band is diagnostic and no alarm is requested. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
         </is>
       </c>
     </row>
@@ -4841,17 +4829,17 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>QuadratureCount</t>
+          <t>PhaseInterpolatedDegrees</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Lock-in quadrature component in ADC counts.</t>
+          <t>Phase used by impedance calibration interpolation.</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.QuadratureCount</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.PhaseInterpolatedDegrees</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
@@ -4861,7 +4849,7 @@
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4876,15 +4864,9 @@
       </c>
       <c r="I48" s="14" t="n"/>
       <c r="J48" s="14" t="n"/>
-      <c r="K48" s="14" t="n">
-        <v>19.048</v>
-      </c>
-      <c r="L48" s="14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M48" s="14" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="K48" s="14" t="n"/>
+      <c r="L48" s="14" t="n"/>
+      <c r="M48" s="14" t="n"/>
       <c r="N48" s="14" t="n"/>
       <c r="O48" s="14" t="n"/>
       <c r="P48" s="14" t="n"/>
@@ -4912,7 +4894,7 @@
       </c>
       <c r="AA48" s="13" t="inlineStr">
         <is>
-          <t>Live controller Q was 19.007..19.083 across 15 coherent completed RUN frames. The desired band is a provisional same-setup trend envelope only. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from unchanged GIZMO.elf PID 1220. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
+          <t>BadNotSupported initially.</t>
         </is>
       </c>
     </row>
@@ -4924,22 +4906,22 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>AveragesPerCalculation</t>
+          <t>InPhaseCount</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Number of acquisitions averaged in each completed calculation.</t>
+          <t>Lock-in in-phase component in ADC counts.</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.AveragesPerCalculation</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.InPhaseCount</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
@@ -4957,20 +4939,16 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I49" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="J49" s="15" t="n">
-        <v>15</v>
-      </c>
+      <c r="I49" s="15" t="n"/>
+      <c r="J49" s="15" t="n"/>
       <c r="K49" s="15" t="n">
-        <v>15</v>
+        <v>-218.931</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>15</v>
+        <v>-220</v>
       </c>
       <c r="M49" s="15" t="n">
-        <v>15</v>
+        <v>-218</v>
       </c>
       <c r="N49" s="15" t="n"/>
       <c r="O49" s="15" t="n"/>
@@ -4991,17 +4969,15 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y49" s="15" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y49" s="15" t="n">
+        <v>1000</v>
       </c>
       <c r="Z49" s="15" t="n">
         <v>1000</v>
       </c>
       <c r="AA49" s="15" t="inlineStr">
         <is>
-          <t>OPC UA built-in type UInt32. Fixed 15 RUN accumulations in the recovered controller; this is not the RUN 3 sleep argument.</t>
+          <t>Live controller I was -219.095..-218.669 across 15 coherent completed RUN frames. The desired band is a provisional same-setup trend envelope only. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
         </is>
       </c>
     </row>
@@ -5013,22 +4989,22 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>QuadratureCount</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Human-readable aggregate quality; clients shall use the OPC UA DataValue StatusCode for logic.</t>
+          <t>Lock-in quadrature component in ADC counts.</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.Quality</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.QuadratureCount</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -5048,9 +5024,15 @@
       </c>
       <c r="I50" s="14" t="n"/>
       <c r="J50" s="14" t="n"/>
-      <c r="K50" s="14" t="n"/>
-      <c r="L50" s="14" t="n"/>
-      <c r="M50" s="14" t="n"/>
+      <c r="K50" s="14" t="n">
+        <v>19.048</v>
+      </c>
+      <c r="L50" s="14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M50" s="14" t="n">
+        <v>19.5</v>
+      </c>
       <c r="N50" s="14" t="n"/>
       <c r="O50" s="14" t="n"/>
       <c r="P50" s="14" t="n"/>
@@ -5070,15 +5052,17 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y50" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y50" s="14" t="n">
+        <v>1000</v>
       </c>
       <c r="Z50" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA50" s="13" t="inlineStr"/>
+      <c r="AA50" s="13" t="inlineStr">
+        <is>
+          <t>Live controller Q was 19.007..19.083 across 15 coherent completed RUN frames. The desired band is a provisional same-setup trend envelope only. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
@@ -5088,22 +5072,22 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>AveragesPerCalculation</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>Bounded diagnostic text explaining degraded or bad data quality.</t>
+          <t>Number of acquisitions averaged in each completed calculation.</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.Diagnostic</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.AveragesPerCalculation</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
@@ -5121,11 +5105,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I51" s="14" t="n"/>
-      <c r="J51" s="14" t="n"/>
-      <c r="K51" s="14" t="n"/>
-      <c r="L51" s="14" t="n"/>
-      <c r="M51" s="14" t="n"/>
+      <c r="I51" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K51" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="L51" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M51" s="14" t="n">
+        <v>15</v>
+      </c>
       <c r="N51" s="14" t="n"/>
       <c r="O51" s="14" t="n"/>
       <c r="P51" s="14" t="n"/>
@@ -5153,7 +5147,11 @@
       <c r="Z51" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA51" s="13" t="inlineStr"/>
+      <c r="AA51" s="13" t="inlineStr">
+        <is>
+          <t>OPC UA built-in type UInt32. Fixed 15 RUN accumulations in the recovered controller; this is not the RUN 3 sleep argument.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="14" t="inlineStr">
@@ -5163,17 +5161,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>LegacyRecord</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Original comma-delimited ZMon record retained for engineering audit only.</t>
+          <t>Human-readable aggregate quality; clients shall use the OPC UA DataValue StatusCode for logic.</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.LegacyRecord</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.Quality</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
@@ -5217,43 +5215,43 @@
       </c>
       <c r="X52" s="14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y52" s="14" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y52" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
       <c r="Z52" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA52" s="13" t="inlineStr">
-        <is>
-          <t>Compatibility/audit field only; it is not a physical-data or parsing contract.</t>
-        </is>
-      </c>
+      <c r="AA52" s="13" t="n"/>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>Alarm</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Authoritative composite alarm decision from the measurement engine.</t>
+          <t>Bounded diagnostic text explaining degraded or bad data quality.</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Alarm.Active</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.Diagnostic</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F53" s="15" t="inlineStr">
@@ -5303,36 +5301,32 @@
       <c r="Z53" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="AA53" s="15" t="inlineStr">
-        <is>
-          <t>The recovered display protocol asserts both alarm-return bits when displayed resistance is below threshold, with no hysteresis or on-delay. The connected board displayed 112 Ohm/green at a live 100-Ohm threshold on 2026-08-12, consistent with the recovered comparison; this does not expose the actual returned status word. The off-board adapter still needs that validated readback; publish BadDataUnavailable until it exists, never a synthesized False. After commissioning, configure Ignition to alarm on Boolean True with 0-s SC on-delay and the same annunciation action shown in the ICD.</t>
-        </is>
-      </c>
+      <c r="AA53" s="15" t="n"/>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Alarm</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Latched</t>
+          <t>LegacyRecord</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Persistent GIZMo alarm latch state.</t>
+          <t>Original comma-delimited ZMon record retained for engineering audit only.</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Alarm.Latched</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Measurement.LegacyRecord</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -5371,20 +5365,16 @@
       </c>
       <c r="X54" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y54" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y54" s="14" t="n"/>
       <c r="Z54" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="AA54" s="13" t="inlineStr">
         <is>
-          <t>BadNotSupported: the recovered legacy controller/display protocol has no Kria-style persistent alarm latch or acknowledge operation.</t>
+          <t>Compatibility/audit field only; it is not a physical-data or parsing contract.</t>
         </is>
       </c>
     </row>
@@ -5396,22 +5386,22 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>Reason supplied by the measurement engine for the composite alarm.</t>
+          <t>Authoritative composite alarm decision from the measurement engine.</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Alarm.Reason</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Alarm.Active</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -5463,7 +5453,7 @@
       </c>
       <c r="AA55" s="13" t="inlineStr">
         <is>
-          <t>BadNotSupported initially: the recovered legacy display return word carries alarm bits but no authoritative reason code.</t>
+          <t>The recovered display protocol asserts alarm-return bits when displayed resistance is below threshold, with no hysteresis or on-delay. The connected board displayed 112 Ohm/green at a 100-Ohm threshold, but that does not expose the actual returned status word. The developing producer shall publish BadDataUnavailable until the authoritative device return is validated; it shall never synthesize False.</t>
         </is>
       </c>
     </row>
@@ -5475,22 +5465,22 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>LatchTime</t>
+          <t>Latched</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Timestamp recorded when the persistent alarm latch was set.</t>
+          <t>Persistent GIZMo alarm latch state.</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Alarm.LatchTime</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Alarm.Latched</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -5542,29 +5532,29 @@
       </c>
       <c r="AA56" s="13" t="inlineStr">
         <is>
-          <t>BadNotSupported: the recovered legacy controller/display protocol has no alarm-latch timestamp.</t>
+          <t>BadNotSupported: the recovered legacy controller/display protocol has no Kria-style persistent alarm latch or acknowledge operation.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>Legacy OPC UA Server</t>
+          <t>Alarm</t>
         </is>
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>RuntimeVersion</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Version of the legacy OPC UA server.</t>
+          <t>Reason supplied by the measurement engine for the composite alarm.</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Firmware.RuntimeVersion</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Alarm.Reason</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
@@ -5617,43 +5607,43 @@
         </is>
       </c>
       <c r="Z57" s="15" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="AA57" s="15" t="inlineStr">
         <is>
-          <t>The production server is under development and its initial release is read-only. The earlier off-board adapter is validation evidence; mutating capabilities below remain staged requirements.</t>
+          <t>BadNotSupported initially: the recovered legacy display return word carries alarm bits but no authoritative reason code.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>Thermal</t>
+          <t>Alarm</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>ChassisTemperatureCelsius</t>
+          <t>LatchTime</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Temperature representative of the legacy GIZMo chassis environment.</t>
+          <t>Timestamp recorded when the persistent alarm latch was set.</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Thermal.ChassisTemperatureCelsius</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Alarm.LatchTime</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -5690,47 +5680,49 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y58" s="14" t="n">
-        <v>1000</v>
+      <c r="Y58" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
       </c>
       <c r="Z58" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="AA58" s="13" t="inlineStr">
         <is>
-          <t>REQUIRED MONITOR VALUE from the Slow Controls analysis. Source and placement require agreement; use a non-good StatusCode and NaN/null until a suitable sensor is validated. Do not substitute Zynq junction temperature without identifying it as a separate variable.</t>
+          <t>BadNotSupported: the recovered legacy controller/display protocol has no alarm-latch timestamp.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Thermal</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>ChassisTemperatureCelsius</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>Legacy calibration readiness.</t>
+          <t>Temperature representative of the legacy GIZMo chassis environment.</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.State</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Thermal.ChassisTemperatureCelsius</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cel</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -5767,39 +5759,37 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y59" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y59" s="14" t="n">
+        <v>1000</v>
       </c>
       <c r="Z59" s="14" t="n">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="AA59" s="13" t="inlineStr">
         <is>
-          <t>Initial value CharacterizationOnly or Unvalidated. Historical CAL files are metadata, not an activated production calibration.</t>
+          <t>REQUIRED MONITOR VALUE from the Slow Controls analysis. Source and placement require agreement; use a non-good StatusCode and NaN/null until a suitable sensor is validated. Do not substitute Zynq junction temperature without identifying it as a separate variable.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Thermal</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>ConfiguredThresholdOhm</t>
+          <t>Cpu1TemperatureCelsius</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Legacy threshold readback used to verify a requested configuration write.</t>
+          <t>CPU temperature sensor 1.</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.ConfiguredThresholdOhm</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Thermal.CPU1TemperatureCelsius</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
@@ -5809,7 +5799,7 @@
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>Ohm</t>
+          <t>Cel</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5822,21 +5812,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I60" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="K60" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="L60" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="M60" s="14" t="n">
-        <v>100</v>
-      </c>
+      <c r="I60" s="14" t="n"/>
+      <c r="J60" s="14" t="n"/>
+      <c r="K60" s="14" t="n"/>
+      <c r="L60" s="14" t="n"/>
+      <c r="M60" s="14" t="n"/>
       <c r="N60" s="14" t="n"/>
       <c r="O60" s="14" t="n"/>
       <c r="P60" s="14" t="n"/>
@@ -5856,49 +5836,47 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y60" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y60" s="14" t="n">
+        <v>1000</v>
       </c>
       <c r="Z60" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="AA60" s="13" t="inlineStr">
         <is>
-          <t>Readback, not a second command path. The requested initial value is 100 Ohm; the controller returned exactly 100 Ohm in every 2026-08-12 direct frame and every 2026-08-13 adapter pilot cycle. Refresh this value from the controller/display after a write.</t>
+          <t>BadNotSupported until a source with defined placement and meaning is validated.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Thermal</t>
         </is>
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>MeasurementsPerCalculation</t>
+          <t>Cpu2TemperatureCelsius</t>
         </is>
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>Observed fixed legacy averaging count.</t>
+          <t>CPU temperature sensor 2.</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.MeasurementsPerCalculation</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Thermal.CPU2TemperatureCelsius</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cel</t>
         </is>
       </c>
       <c r="G61" s="15" t="inlineStr">
@@ -5911,21 +5889,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I61" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="J61" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="K61" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="L61" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="M61" s="15" t="n">
-        <v>15</v>
-      </c>
+      <c r="I61" s="15" t="n"/>
+      <c r="J61" s="15" t="n"/>
+      <c r="K61" s="15" t="n"/>
+      <c r="L61" s="15" t="n"/>
+      <c r="M61" s="15" t="n"/>
       <c r="N61" s="15" t="n"/>
       <c r="O61" s="15" t="n"/>
       <c r="P61" s="15" t="n"/>
@@ -5945,49 +5913,47 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y61" s="15" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y61" s="15" t="n">
+        <v>1000</v>
       </c>
       <c r="Z61" s="15" t="n">
         <v>1000</v>
       </c>
       <c r="AA61" s="15" t="inlineStr">
         <is>
-          <t>OPC UA built-in type UInt32. Fixed 15 RUN accumulations in the recovered controller and confirmed in every live 2026-08-12 frame.</t>
+          <t>BadNotSupported until a source with defined placement and meaning is validated.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Thermal</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>AveragesPerCalculation</t>
+          <t>Cpu3TemperatureCelsius</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Legacy endpoint compatibility node; fixed/read-only in the initial release.</t>
+          <t>CPU temperature sensor 3.</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Configuration.AveragesPerCalculation</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Thermal.CPU3TemperatureCelsius</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cel</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -6000,21 +5966,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I62" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="J62" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K62" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="L62" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="M62" s="14" t="n">
-        <v>15</v>
-      </c>
+      <c r="I62" s="14" t="n"/>
+      <c r="J62" s="14" t="n"/>
+      <c r="K62" s="14" t="n"/>
+      <c r="L62" s="14" t="n"/>
+      <c r="M62" s="14" t="n"/>
       <c r="N62" s="14" t="n"/>
       <c r="O62" s="14" t="n"/>
       <c r="P62" s="14" t="n"/>
@@ -6034,44 +5990,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y62" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y62" s="14" t="n">
+        <v>1000</v>
       </c>
       <c r="Z62" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="AA62" s="13" t="inlineStr">
         <is>
-          <t>OPC UA built-in type UInt32. Fixed 15 RUN accumulations, confirmed live on 2026-08-12; the RUN argument controls cadence and is not averaging.</t>
+          <t>BadNotSupported until a source with defined placement and meaning is validated.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>LastCommandResult</t>
+          <t>NtpSynchronized</t>
         </is>
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>Model-1.3 compatibility result for the most recent accepted or rejected write/method.</t>
+          <t>True only while current-boot target SNTP evidence remains within the 15-minute holdover bound.</t>
         </is>
       </c>
       <c r="D63" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Configuration.LastCommandResult</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Time.NtpSynchronized</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -6123,34 +6077,34 @@
       </c>
       <c r="AA63" s="13" t="inlineStr">
         <is>
-          <t>Keep for compatibility; model-1.4 Operations command-status nodes are the complete audit/readback contract.</t>
+          <t>REQUIRED MODEL 1.3.1 TIME STATUS; implementation and current-boot evidence remain under development/verification. Publish a non-good StatusCode until the stated condition is measured; service activity alone is not proof of synchronization.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>NtpServiceActive</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Aggregate endpoint health: OK, Degraded, Failed, or Starting.</t>
+          <t>True when the legacy target gizmo-time-sync service process is alive.</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Overall</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Time.NtpServiceActive</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -6200,32 +6154,36 @@
       <c r="Z64" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA64" s="13" t="inlineStr"/>
+      <c r="AA64" s="13" t="inlineStr">
+        <is>
+          <t>REQUIRED MODEL 1.3.1 TIME STATUS; implementation and current-boot evidence remain under development/verification. Publish a non-good StatusCode until the stated condition is measured; service activity alone is not proof of synchronization.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>LastUpdate</t>
+          <t>NtpService</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Time aggregate health was last evaluated.</t>
+          <t>Bounded identification of the legacy SNTP client and workstation source.</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.LastUpdate</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Time.NtpService</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
@@ -6267,43 +6225,49 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y65" s="15" t="n">
-        <v>1000</v>
+      <c r="Y65" s="15" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
       </c>
       <c r="Z65" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA65" s="15" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="AA65" s="15" t="inlineStr">
+        <is>
+          <t>REQUIRED MODEL 1.3.1 TIME STATUS; implementation and current-boot evidence remain under development/verification. Publish a non-good StatusCode until the stated condition is measured; service activity alone is not proof of synchronization.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>UptimeSeconds</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of the measurement subtree.</t>
+          <t>Linux uptime.</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Measurement</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Time.UptimeSeconds</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -6340,45 +6304,47 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y66" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y66" s="14" t="n">
+        <v>10000</v>
       </c>
       <c r="Z66" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA66" s="13" t="inlineStr"/>
+      <c r="AA66" s="13" t="inlineStr">
+        <is>
+          <t>Required model 1.3.1 value; implementation is under development and must report non-good quality until available.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>OperatingSystem</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Thermal</t>
+          <t>CpuUtilizationPercent</t>
         </is>
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of the thermal subtree.</t>
+          <t>CPU utilization between samples.</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Thermal</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.OperatingSystem.CpuUtilizationPercent</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -6415,49 +6381,47 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y67" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y67" s="14" t="n">
+        <v>10000</v>
       </c>
       <c r="Z67" s="14" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AA67" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Required model 1.3.1 value; implementation is under development and must report non-good quality until available.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>OperatingSystem</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>MemoryAvailableBytes</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of timekeeping.</t>
+          <t>Physical memory available without swapping.</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Time</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.OperatingSystem.MemoryAvailableBytes</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>byte</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -6494,39 +6458,37 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y68" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
+      <c r="Y68" s="14" t="n">
+        <v>10000</v>
       </c>
       <c r="Z68" s="14" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AA68" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Required model 1.3.1 value; implementation is under development and must report non-good quality until available.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Firmware</t>
         </is>
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>OperatingSystem</t>
+          <t>RuntimeVersion</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Aggregate quality of operating-system telemetry.</t>
+          <t>Version of this implementation's GIZMo runtime/OPC UA producer.</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.OperatingSystem</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Firmware.RuntimeVersion</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
@@ -6583,29 +6545,29 @@
       </c>
       <c r="AA69" s="15" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>ZedBoard producer under development; publish the installed runtime version only when the running artifact identity is verified. This revision makes no deployment or control-acceptance claim.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Firmware</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>OverlayState</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of network monitoring.</t>
+          <t>State of this implementation's controlled programmable-logic image.</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Network</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Firmware.OverlayState</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -6658,33 +6620,33 @@
         </is>
       </c>
       <c r="Z70" s="14" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="AA70" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Required model 1.3.1 value; map to the controlled ZedBoard programmable-logic state without changing its meaning.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Firmware</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>OverlayBitstreamSha256</t>
         </is>
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of storage monitoring.</t>
+          <t>SHA-256 digest of this implementation's controlled programmable-logic image.</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Storage</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Firmware.OverlayBitstreamSha256</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -6728,42 +6690,38 @@
       </c>
       <c r="X71" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y71" s="14" t="inlineStr">
-        <is>
-          <t>On-Change</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y71" s="14" t="n"/>
       <c r="Z71" s="14" t="n">
         <v>30000</v>
       </c>
       <c r="AA71" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Required model 1.3.1 value; publish the controlled ZedBoard bitstream digest or non-good quality, never a Kria digest.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Firmware</t>
+          <t>State</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of runtime and programmable-logic state.</t>
+          <t>Legacy calibration readiness.</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Firmware</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.State</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -6820,39 +6778,39 @@
       </c>
       <c r="AA72" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Initial value CharacterizationOnly or Unvalidated. Historical CAL files are metadata, not an activated production calibration.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>ConfiguredThresholdOhm</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Aggregate quality of owned legacy OPC UA server processes.</t>
+          <t>Legacy threshold readback used to verify a requested configuration write.</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Services</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.ConfiguredThresholdOhm</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Ohm</t>
         </is>
       </c>
       <c r="G73" s="15" t="inlineStr">
@@ -6865,11 +6823,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I73" s="15" t="n"/>
-      <c r="J73" s="15" t="n"/>
-      <c r="K73" s="15" t="n"/>
-      <c r="L73" s="15" t="n"/>
-      <c r="M73" s="15" t="n"/>
+      <c r="I73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="15" t="n">
+        <v>1023</v>
+      </c>
+      <c r="K73" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="L73" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="M73" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="N73" s="15" t="n"/>
       <c r="O73" s="15" t="n"/>
       <c r="P73" s="15" t="n"/>
@@ -6895,38 +6863,38 @@
         </is>
       </c>
       <c r="Z73" s="15" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="AA73" s="15" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>Readback, not a second command path. Requested initial value is 100 Ohm. The common model-1.3.1 range and recovered controller field are both 0..1023. Publish from a coherent record; writes remain disabled until accepted.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>MeasurementsPerCalculation</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of calibration metadata.</t>
+          <t>Observed fixed legacy averaging count.</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Calibration</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.MeasurementsPerCalculation</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6944,11 +6912,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I74" s="14" t="n"/>
-      <c r="J74" s="14" t="n"/>
-      <c r="K74" s="14" t="n"/>
-      <c r="L74" s="14" t="n"/>
-      <c r="M74" s="14" t="n"/>
+      <c r="I74" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="J74" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K74" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="L74" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M74" s="14" t="n">
+        <v>15</v>
+      </c>
       <c r="N74" s="14" t="n"/>
       <c r="O74" s="14" t="n"/>
       <c r="P74" s="14" t="n"/>
@@ -6974,38 +6952,38 @@
         </is>
       </c>
       <c r="Z74" s="14" t="n">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="AA74" s="13" t="inlineStr">
         <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
+          <t>OPC UA built-in type UInt32. Fixed 15 RUN accumulations in the recovered controller and confirmed in every live 2026-08-12 frame.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>SDR</t>
+          <t>LastCalibrationTime</t>
         </is>
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>Aggregate quality of SDR acquisition.</t>
+          <t>Newest modification time among production calibration tables.</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.SDR</t>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Calibration.LastCalibrationTime</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
@@ -7053,390 +7031,1026 @@
         </is>
       </c>
       <c r="Z75" s="14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA75" s="13" t="inlineStr">
+        <is>
+          <t>BadDataUnavailable while calibration remains CharacterizationOnly/Unvalidated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>LastCommandResult</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Result of the most recent accepted or rejected canonical write.</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Configuration.LastCommandResult</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="n"/>
+      <c r="J76" s="14" t="n"/>
+      <c r="K76" s="14" t="n"/>
+      <c r="L76" s="14" t="n"/>
+      <c r="M76" s="14" t="n"/>
+      <c r="N76" s="14" t="n"/>
+      <c r="O76" s="14" t="n"/>
+      <c r="P76" s="14" t="n"/>
+      <c r="Q76" s="14" t="n"/>
+      <c r="R76" s="14" t="n"/>
+      <c r="S76" s="14" t="n"/>
+      <c r="T76" s="14" t="n"/>
+      <c r="U76" s="14" t="n"/>
+      <c r="V76" s="14" t="n"/>
+      <c r="W76" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X76" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y76" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z76" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA75" s="13" t="inlineStr">
-        <is>
-          <t>Quality refers to the legacy OPC UA server or available target metadata; unsupported target details remain explicit as NotAvailable/BadNotSupported rather than being synthesized.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="n"/>
-      <c r="B76" s="11" t="n"/>
-      <c r="C76" s="11" t="n"/>
-      <c r="D76" s="11" t="n"/>
-      <c r="E76" s="11" t="n"/>
-      <c r="F76" s="11" t="n"/>
-      <c r="G76" s="11" t="n"/>
-      <c r="H76" s="11" t="n"/>
-      <c r="I76" s="11" t="n"/>
-      <c r="J76" s="11" t="n"/>
-      <c r="K76" s="11" t="n"/>
-      <c r="L76" s="11" t="n"/>
-      <c r="M76" s="11" t="n"/>
-      <c r="N76" s="11" t="n"/>
-      <c r="O76" s="11" t="n"/>
-      <c r="P76" s="11" t="n"/>
-      <c r="Q76" s="11" t="n"/>
-      <c r="R76" s="11" t="n"/>
-      <c r="S76" s="11" t="n"/>
-      <c r="T76" s="11" t="n"/>
-      <c r="U76" s="11" t="n"/>
-      <c r="V76" s="11" t="n"/>
-      <c r="W76" s="11" t="n"/>
-      <c r="X76" s="11" t="n"/>
-      <c r="Y76" s="11" t="n"/>
-      <c r="Z76" s="11" t="n"/>
-      <c r="AA76" s="11" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="n"/>
-      <c r="B77" s="11" t="n"/>
-      <c r="C77" s="11" t="n"/>
-      <c r="D77" s="11" t="n"/>
-      <c r="E77" s="11" t="n"/>
-      <c r="F77" s="11" t="n"/>
-      <c r="G77" s="11" t="n"/>
-      <c r="H77" s="11" t="n"/>
-      <c r="I77" s="11" t="n"/>
-      <c r="J77" s="11" t="n"/>
-      <c r="K77" s="11" t="n"/>
-      <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n"/>
-      <c r="O77" s="11" t="n"/>
-      <c r="P77" s="11" t="n"/>
-      <c r="Q77" s="11" t="n"/>
-      <c r="R77" s="11" t="n"/>
-      <c r="S77" s="11" t="n"/>
-      <c r="T77" s="11" t="n"/>
-      <c r="U77" s="11" t="n"/>
-      <c r="V77" s="11" t="n"/>
-      <c r="W77" s="11" t="n"/>
-      <c r="X77" s="11" t="n"/>
-      <c r="Y77" s="11" t="n"/>
-      <c r="Z77" s="11" t="n"/>
-      <c r="AA77" s="11" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="n"/>
-      <c r="B78" s="11" t="n"/>
-      <c r="C78" s="11" t="n"/>
-      <c r="D78" s="11" t="n"/>
-      <c r="E78" s="11" t="n"/>
-      <c r="F78" s="11" t="n"/>
-      <c r="G78" s="11" t="n"/>
-      <c r="H78" s="11" t="n"/>
-      <c r="I78" s="11" t="n"/>
-      <c r="J78" s="11" t="n"/>
-      <c r="K78" s="11" t="n"/>
-      <c r="L78" s="11" t="n"/>
-      <c r="M78" s="11" t="n"/>
-      <c r="N78" s="11" t="n"/>
-      <c r="O78" s="11" t="n"/>
-      <c r="P78" s="11" t="n"/>
-      <c r="Q78" s="11" t="n"/>
-      <c r="R78" s="11" t="n"/>
-      <c r="S78" s="11" t="n"/>
-      <c r="T78" s="11" t="n"/>
-      <c r="U78" s="11" t="n"/>
-      <c r="V78" s="11" t="n"/>
-      <c r="W78" s="11" t="n"/>
-      <c r="X78" s="11" t="n"/>
-      <c r="Y78" s="11" t="n"/>
-      <c r="Z78" s="11" t="n"/>
-      <c r="AA78" s="11" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="n"/>
-      <c r="B79" s="11" t="n"/>
-      <c r="C79" s="11" t="n"/>
-      <c r="D79" s="11" t="n"/>
-      <c r="E79" s="11" t="n"/>
-      <c r="F79" s="11" t="n"/>
-      <c r="G79" s="11" t="n"/>
-      <c r="H79" s="11" t="n"/>
-      <c r="I79" s="11" t="n"/>
-      <c r="J79" s="11" t="n"/>
-      <c r="K79" s="11" t="n"/>
-      <c r="L79" s="11" t="n"/>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="11" t="n"/>
-      <c r="O79" s="11" t="n"/>
-      <c r="P79" s="11" t="n"/>
-      <c r="Q79" s="11" t="n"/>
-      <c r="R79" s="11" t="n"/>
-      <c r="S79" s="11" t="n"/>
-      <c r="T79" s="11" t="n"/>
-      <c r="U79" s="11" t="n"/>
-      <c r="V79" s="11" t="n"/>
-      <c r="W79" s="11" t="n"/>
-      <c r="X79" s="11" t="n"/>
-      <c r="Y79" s="11" t="n"/>
-      <c r="Z79" s="11" t="n"/>
-      <c r="AA79" s="11" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="11" t="n"/>
-      <c r="B80" s="11" t="n"/>
-      <c r="C80" s="11" t="n"/>
-      <c r="D80" s="11" t="n"/>
-      <c r="E80" s="11" t="n"/>
-      <c r="F80" s="11" t="n"/>
-      <c r="G80" s="11" t="n"/>
-      <c r="H80" s="11" t="n"/>
-      <c r="I80" s="11" t="n"/>
-      <c r="J80" s="11" t="n"/>
-      <c r="K80" s="11" t="n"/>
-      <c r="L80" s="11" t="n"/>
-      <c r="M80" s="11" t="n"/>
-      <c r="N80" s="11" t="n"/>
-      <c r="O80" s="11" t="n"/>
-      <c r="P80" s="11" t="n"/>
-      <c r="Q80" s="11" t="n"/>
-      <c r="R80" s="11" t="n"/>
-      <c r="S80" s="11" t="n"/>
-      <c r="T80" s="11" t="n"/>
-      <c r="U80" s="11" t="n"/>
-      <c r="V80" s="11" t="n"/>
-      <c r="W80" s="11" t="n"/>
-      <c r="X80" s="11" t="n"/>
-      <c r="Y80" s="11" t="n"/>
-      <c r="Z80" s="11" t="n"/>
-      <c r="AA80" s="11" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="n"/>
-      <c r="B81" s="11" t="n"/>
-      <c r="C81" s="11" t="n"/>
-      <c r="D81" s="11" t="n"/>
-      <c r="E81" s="11" t="n"/>
-      <c r="F81" s="11" t="n"/>
-      <c r="G81" s="11" t="n"/>
-      <c r="H81" s="11" t="n"/>
-      <c r="I81" s="11" t="n"/>
-      <c r="J81" s="11" t="n"/>
-      <c r="K81" s="11" t="n"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
-      <c r="O81" s="11" t="n"/>
-      <c r="P81" s="11" t="n"/>
-      <c r="Q81" s="11" t="n"/>
-      <c r="R81" s="11" t="n"/>
-      <c r="S81" s="11" t="n"/>
-      <c r="T81" s="11" t="n"/>
-      <c r="U81" s="11" t="n"/>
-      <c r="V81" s="11" t="n"/>
-      <c r="W81" s="11" t="n"/>
-      <c r="X81" s="11" t="n"/>
-      <c r="Y81" s="11" t="n"/>
-      <c r="Z81" s="11" t="n"/>
-      <c r="AA81" s="11" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="11" t="n"/>
-      <c r="B82" s="11" t="n"/>
-      <c r="C82" s="11" t="n"/>
-      <c r="D82" s="11" t="n"/>
-      <c r="E82" s="11" t="n"/>
-      <c r="F82" s="11" t="n"/>
-      <c r="G82" s="11" t="n"/>
-      <c r="H82" s="11" t="n"/>
-      <c r="I82" s="11" t="n"/>
-      <c r="J82" s="11" t="n"/>
-      <c r="K82" s="11" t="n"/>
-      <c r="L82" s="11" t="n"/>
-      <c r="M82" s="11" t="n"/>
-      <c r="N82" s="11" t="n"/>
-      <c r="O82" s="11" t="n"/>
-      <c r="P82" s="11" t="n"/>
-      <c r="Q82" s="11" t="n"/>
-      <c r="R82" s="11" t="n"/>
-      <c r="S82" s="11" t="n"/>
-      <c r="T82" s="11" t="n"/>
-      <c r="U82" s="11" t="n"/>
-      <c r="V82" s="11" t="n"/>
-      <c r="W82" s="11" t="n"/>
-      <c r="X82" s="11" t="n"/>
-      <c r="Y82" s="11" t="n"/>
-      <c r="Z82" s="11" t="n"/>
-      <c r="AA82" s="11" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="11" t="n"/>
-      <c r="B83" s="11" t="n"/>
-      <c r="C83" s="11" t="n"/>
-      <c r="D83" s="11" t="n"/>
-      <c r="E83" s="11" t="n"/>
-      <c r="F83" s="11" t="n"/>
-      <c r="G83" s="11" t="n"/>
-      <c r="H83" s="11" t="n"/>
-      <c r="I83" s="11" t="n"/>
-      <c r="J83" s="11" t="n"/>
-      <c r="K83" s="11" t="n"/>
-      <c r="L83" s="11" t="n"/>
-      <c r="M83" s="11" t="n"/>
-      <c r="N83" s="11" t="n"/>
-      <c r="O83" s="11" t="n"/>
-      <c r="P83" s="11" t="n"/>
-      <c r="Q83" s="11" t="n"/>
-      <c r="R83" s="11" t="n"/>
-      <c r="S83" s="11" t="n"/>
-      <c r="T83" s="11" t="n"/>
-      <c r="U83" s="11" t="n"/>
-      <c r="V83" s="11" t="n"/>
-      <c r="W83" s="11" t="n"/>
-      <c r="X83" s="11" t="n"/>
-      <c r="Y83" s="11" t="n"/>
-      <c r="Z83" s="11" t="n"/>
-      <c r="AA83" s="11" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="11" t="n"/>
-      <c r="B84" s="11" t="n"/>
-      <c r="C84" s="11" t="n"/>
-      <c r="D84" s="11" t="n"/>
-      <c r="E84" s="11" t="n"/>
-      <c r="F84" s="11" t="n"/>
-      <c r="G84" s="11" t="n"/>
-      <c r="H84" s="11" t="n"/>
-      <c r="I84" s="11" t="n"/>
-      <c r="J84" s="11" t="n"/>
-      <c r="K84" s="11" t="n"/>
-      <c r="L84" s="11" t="n"/>
-      <c r="M84" s="11" t="n"/>
-      <c r="N84" s="11" t="n"/>
-      <c r="O84" s="11" t="n"/>
-      <c r="P84" s="11" t="n"/>
-      <c r="Q84" s="11" t="n"/>
-      <c r="R84" s="11" t="n"/>
-      <c r="S84" s="11" t="n"/>
-      <c r="T84" s="11" t="n"/>
-      <c r="U84" s="11" t="n"/>
-      <c r="V84" s="11" t="n"/>
-      <c r="W84" s="11" t="n"/>
-      <c r="X84" s="11" t="n"/>
-      <c r="Y84" s="11" t="n"/>
-      <c r="Z84" s="11" t="n"/>
-      <c r="AA84" s="11" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="11" t="n"/>
-      <c r="B85" s="11" t="n"/>
-      <c r="C85" s="11" t="n"/>
-      <c r="D85" s="11" t="n"/>
-      <c r="E85" s="11" t="n"/>
-      <c r="F85" s="11" t="n"/>
-      <c r="G85" s="11" t="n"/>
-      <c r="H85" s="11" t="n"/>
-      <c r="I85" s="11" t="n"/>
-      <c r="J85" s="11" t="n"/>
-      <c r="K85" s="11" t="n"/>
-      <c r="L85" s="11" t="n"/>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="11" t="n"/>
-      <c r="O85" s="11" t="n"/>
-      <c r="P85" s="11" t="n"/>
-      <c r="Q85" s="11" t="n"/>
-      <c r="R85" s="11" t="n"/>
-      <c r="S85" s="11" t="n"/>
-      <c r="T85" s="11" t="n"/>
-      <c r="U85" s="11" t="n"/>
-      <c r="V85" s="11" t="n"/>
-      <c r="W85" s="11" t="n"/>
-      <c r="X85" s="11" t="n"/>
-      <c r="Y85" s="11" t="n"/>
-      <c r="Z85" s="11" t="n"/>
-      <c r="AA85" s="11" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="11" t="n"/>
-      <c r="B86" s="11" t="n"/>
-      <c r="C86" s="11" t="n"/>
-      <c r="D86" s="11" t="n"/>
-      <c r="E86" s="11" t="n"/>
-      <c r="F86" s="11" t="n"/>
-      <c r="G86" s="11" t="n"/>
-      <c r="H86" s="11" t="n"/>
-      <c r="I86" s="11" t="n"/>
-      <c r="J86" s="11" t="n"/>
-      <c r="K86" s="11" t="n"/>
-      <c r="L86" s="11" t="n"/>
-      <c r="M86" s="11" t="n"/>
-      <c r="N86" s="11" t="n"/>
-      <c r="O86" s="11" t="n"/>
-      <c r="P86" s="11" t="n"/>
-      <c r="Q86" s="11" t="n"/>
-      <c r="R86" s="11" t="n"/>
-      <c r="S86" s="11" t="n"/>
-      <c r="T86" s="11" t="n"/>
-      <c r="U86" s="11" t="n"/>
-      <c r="V86" s="11" t="n"/>
-      <c r="W86" s="11" t="n"/>
-      <c r="X86" s="11" t="n"/>
-      <c r="Y86" s="11" t="n"/>
-      <c r="Z86" s="11" t="n"/>
-      <c r="AA86" s="11" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="11" t="n"/>
-      <c r="B87" s="11" t="n"/>
-      <c r="C87" s="11" t="n"/>
-      <c r="D87" s="11" t="n"/>
-      <c r="E87" s="11" t="n"/>
-      <c r="F87" s="11" t="n"/>
-      <c r="G87" s="11" t="n"/>
-      <c r="H87" s="11" t="n"/>
-      <c r="I87" s="11" t="n"/>
-      <c r="J87" s="11" t="n"/>
-      <c r="K87" s="11" t="n"/>
-      <c r="L87" s="11" t="n"/>
-      <c r="M87" s="11" t="n"/>
-      <c r="N87" s="11" t="n"/>
-      <c r="O87" s="11" t="n"/>
-      <c r="P87" s="11" t="n"/>
-      <c r="Q87" s="11" t="n"/>
-      <c r="R87" s="11" t="n"/>
-      <c r="S87" s="11" t="n"/>
-      <c r="T87" s="11" t="n"/>
-      <c r="U87" s="11" t="n"/>
-      <c r="V87" s="11" t="n"/>
-      <c r="W87" s="11" t="n"/>
-      <c r="X87" s="11" t="n"/>
-      <c r="Y87" s="11" t="n"/>
-      <c r="Z87" s="11" t="n"/>
-      <c r="AA87" s="11" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="11" t="n"/>
-      <c r="B88" s="11" t="n"/>
-      <c r="C88" s="11" t="n"/>
-      <c r="D88" s="11" t="n"/>
-      <c r="E88" s="11" t="n"/>
-      <c r="F88" s="11" t="n"/>
-      <c r="G88" s="11" t="n"/>
-      <c r="H88" s="11" t="n"/>
-      <c r="I88" s="11" t="n"/>
-      <c r="J88" s="11" t="n"/>
-      <c r="K88" s="11" t="n"/>
-      <c r="L88" s="11" t="n"/>
-      <c r="M88" s="11" t="n"/>
-      <c r="N88" s="11" t="n"/>
-      <c r="O88" s="11" t="n"/>
-      <c r="P88" s="11" t="n"/>
-      <c r="Q88" s="11" t="n"/>
-      <c r="R88" s="11" t="n"/>
-      <c r="S88" s="11" t="n"/>
-      <c r="T88" s="11" t="n"/>
-      <c r="U88" s="11" t="n"/>
-      <c r="V88" s="11" t="n"/>
-      <c r="W88" s="11" t="n"/>
-      <c r="X88" s="11" t="n"/>
-      <c r="Y88" s="11" t="n"/>
-      <c r="Z88" s="11" t="n"/>
-      <c r="AA88" s="11" t="n"/>
+      <c r="AA76" s="13" t="inlineStr">
+        <is>
+          <t>Canonical model-1.3.1 readback. Because the initial ZedBoard profile is monitoring-only, report rejected/unsupported attempts according to the server library without implying that a mutation was accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Aggregate endpoint health: OK, Degraded, Failed, or Starting.</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Overall</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I77" s="15" t="n"/>
+      <c r="J77" s="15" t="n"/>
+      <c r="K77" s="15" t="n"/>
+      <c r="L77" s="15" t="n"/>
+      <c r="M77" s="15" t="n"/>
+      <c r="N77" s="15" t="n"/>
+      <c r="O77" s="15" t="n"/>
+      <c r="P77" s="15" t="n"/>
+      <c r="Q77" s="15" t="n"/>
+      <c r="R77" s="15" t="n"/>
+      <c r="S77" s="15" t="n"/>
+      <c r="T77" s="15" t="n"/>
+      <c r="U77" s="15" t="n"/>
+      <c r="V77" s="15" t="n"/>
+      <c r="W77" s="15" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X77" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y77" s="15" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z77" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA77" s="15" t="n"/>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>LastUpdate</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Time aggregate health was last evaluated.</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.LastUpdate</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="n"/>
+      <c r="J78" s="14" t="n"/>
+      <c r="K78" s="14" t="n"/>
+      <c r="L78" s="14" t="n"/>
+      <c r="M78" s="14" t="n"/>
+      <c r="N78" s="14" t="n"/>
+      <c r="O78" s="14" t="n"/>
+      <c r="P78" s="14" t="n"/>
+      <c r="Q78" s="14" t="n"/>
+      <c r="R78" s="14" t="n"/>
+      <c r="S78" s="14" t="n"/>
+      <c r="T78" s="14" t="n"/>
+      <c r="U78" s="14" t="n"/>
+      <c r="V78" s="14" t="n"/>
+      <c r="W78" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X78" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y78" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z78" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA78" s="13" t="n"/>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of the measurement subtree.</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Measurement</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I79" s="14" t="n"/>
+      <c r="J79" s="14" t="n"/>
+      <c r="K79" s="14" t="n"/>
+      <c r="L79" s="14" t="n"/>
+      <c r="M79" s="14" t="n"/>
+      <c r="N79" s="14" t="n"/>
+      <c r="O79" s="14" t="n"/>
+      <c r="P79" s="14" t="n"/>
+      <c r="Q79" s="14" t="n"/>
+      <c r="R79" s="14" t="n"/>
+      <c r="S79" s="14" t="n"/>
+      <c r="T79" s="14" t="n"/>
+      <c r="U79" s="14" t="n"/>
+      <c r="V79" s="14" t="n"/>
+      <c r="W79" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X79" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y79" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z79" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA79" s="13" t="n"/>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Thermal</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of the thermal subtree.</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Thermal</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="n"/>
+      <c r="J80" s="14" t="n"/>
+      <c r="K80" s="14" t="n"/>
+      <c r="L80" s="14" t="n"/>
+      <c r="M80" s="14" t="n"/>
+      <c r="N80" s="14" t="n"/>
+      <c r="O80" s="14" t="n"/>
+      <c r="P80" s="14" t="n"/>
+      <c r="Q80" s="14" t="n"/>
+      <c r="R80" s="14" t="n"/>
+      <c r="S80" s="14" t="n"/>
+      <c r="T80" s="14" t="n"/>
+      <c r="U80" s="14" t="n"/>
+      <c r="V80" s="14" t="n"/>
+      <c r="W80" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X80" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y80" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z80" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA80" s="13" t="inlineStr">
+        <is>
+          <t>Aggregate only actual ZedBoard producer inputs. Unsupported or unavailable details remain explicit as NotAvailable/BadNotSupported and are never synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Aggregate quality of timekeeping.</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Time</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="n"/>
+      <c r="J81" s="15" t="n"/>
+      <c r="K81" s="15" t="n"/>
+      <c r="L81" s="15" t="n"/>
+      <c r="M81" s="15" t="n"/>
+      <c r="N81" s="15" t="n"/>
+      <c r="O81" s="15" t="n"/>
+      <c r="P81" s="15" t="n"/>
+      <c r="Q81" s="15" t="n"/>
+      <c r="R81" s="15" t="n"/>
+      <c r="S81" s="15" t="n"/>
+      <c r="T81" s="15" t="n"/>
+      <c r="U81" s="15" t="n"/>
+      <c r="V81" s="15" t="n"/>
+      <c r="W81" s="15" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X81" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y81" s="15" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z81" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA81" s="15" t="inlineStr">
+        <is>
+          <t>Aggregate only actual ZedBoard producer inputs. Unsupported or unavailable details remain explicit as NotAvailable/BadNotSupported and are never synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>OperatingSystem</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of operating-system telemetry.</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.OperatingSystem</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I82" s="14" t="n"/>
+      <c r="J82" s="14" t="n"/>
+      <c r="K82" s="14" t="n"/>
+      <c r="L82" s="14" t="n"/>
+      <c r="M82" s="14" t="n"/>
+      <c r="N82" s="14" t="n"/>
+      <c r="O82" s="14" t="n"/>
+      <c r="P82" s="14" t="n"/>
+      <c r="Q82" s="14" t="n"/>
+      <c r="R82" s="14" t="n"/>
+      <c r="S82" s="14" t="n"/>
+      <c r="T82" s="14" t="n"/>
+      <c r="U82" s="14" t="n"/>
+      <c r="V82" s="14" t="n"/>
+      <c r="W82" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X82" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y82" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z82" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AA82" s="13" t="inlineStr">
+        <is>
+          <t>Aggregate only actual ZedBoard producer inputs. Unsupported or unavailable details remain explicit as NotAvailable/BadNotSupported and are never synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of network monitoring.</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Network</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="n"/>
+      <c r="J83" s="14" t="n"/>
+      <c r="K83" s="14" t="n"/>
+      <c r="L83" s="14" t="n"/>
+      <c r="M83" s="14" t="n"/>
+      <c r="N83" s="14" t="n"/>
+      <c r="O83" s="14" t="n"/>
+      <c r="P83" s="14" t="n"/>
+      <c r="Q83" s="14" t="n"/>
+      <c r="R83" s="14" t="n"/>
+      <c r="S83" s="14" t="n"/>
+      <c r="T83" s="14" t="n"/>
+      <c r="U83" s="14" t="n"/>
+      <c r="V83" s="14" t="n"/>
+      <c r="W83" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X83" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y83" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z83" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AA83" s="13" t="inlineStr">
+        <is>
+          <t>Aggregate only actual ZedBoard producer inputs. Unsupported or unavailable details remain explicit as NotAvailable/BadNotSupported and are never synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of storage monitoring.</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Storage</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H84" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I84" s="14" t="n"/>
+      <c r="J84" s="14" t="n"/>
+      <c r="K84" s="14" t="n"/>
+      <c r="L84" s="14" t="n"/>
+      <c r="M84" s="14" t="n"/>
+      <c r="N84" s="14" t="n"/>
+      <c r="O84" s="14" t="n"/>
+      <c r="P84" s="14" t="n"/>
+      <c r="Q84" s="14" t="n"/>
+      <c r="R84" s="14" t="n"/>
+      <c r="S84" s="14" t="n"/>
+      <c r="T84" s="14" t="n"/>
+      <c r="U84" s="14" t="n"/>
+      <c r="V84" s="14" t="n"/>
+      <c r="W84" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X84" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y84" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z84" s="14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA84" s="13" t="inlineStr">
+        <is>
+          <t>Aggregate only actual ZedBoard producer inputs. Unsupported or unavailable details remain explicit as NotAvailable/BadNotSupported and are never synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="42" customHeight="1">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>Aggregate quality of runtime and programmable-logic state.</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Firmware</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I85" s="15" t="n"/>
+      <c r="J85" s="15" t="n"/>
+      <c r="K85" s="15" t="n"/>
+      <c r="L85" s="15" t="n"/>
+      <c r="M85" s="15" t="n"/>
+      <c r="N85" s="15" t="n"/>
+      <c r="O85" s="15" t="n"/>
+      <c r="P85" s="15" t="n"/>
+      <c r="Q85" s="15" t="n"/>
+      <c r="R85" s="15" t="n"/>
+      <c r="S85" s="15" t="n"/>
+      <c r="T85" s="15" t="n"/>
+      <c r="U85" s="15" t="n"/>
+      <c r="V85" s="15" t="n"/>
+      <c r="W85" s="15" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X85" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y85" s="15" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z85" s="15" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA85" s="15" t="inlineStr">
+        <is>
+          <t>Aggregate only actual ZedBoard producer inputs. Unsupported or unavailable details remain explicit as NotAvailable/BadNotSupported and are never synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of owned services or adapter processes.</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Services</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H86" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I86" s="14" t="n"/>
+      <c r="J86" s="14" t="n"/>
+      <c r="K86" s="14" t="n"/>
+      <c r="L86" s="14" t="n"/>
+      <c r="M86" s="14" t="n"/>
+      <c r="N86" s="14" t="n"/>
+      <c r="O86" s="14" t="n"/>
+      <c r="P86" s="14" t="n"/>
+      <c r="Q86" s="14" t="n"/>
+      <c r="R86" s="14" t="n"/>
+      <c r="S86" s="14" t="n"/>
+      <c r="T86" s="14" t="n"/>
+      <c r="U86" s="14" t="n"/>
+      <c r="V86" s="14" t="n"/>
+      <c r="W86" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X86" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y86" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z86" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AA86" s="13" t="inlineStr">
+        <is>
+          <t>Aggregate only actual ZedBoard producer inputs. Unsupported or unavailable details remain explicit as NotAvailable/BadNotSupported and are never synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of calibration metadata.</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.Calibration</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H87" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I87" s="14" t="n"/>
+      <c r="J87" s="14" t="n"/>
+      <c r="K87" s="14" t="n"/>
+      <c r="L87" s="14" t="n"/>
+      <c r="M87" s="14" t="n"/>
+      <c r="N87" s="14" t="n"/>
+      <c r="O87" s="14" t="n"/>
+      <c r="P87" s="14" t="n"/>
+      <c r="Q87" s="14" t="n"/>
+      <c r="R87" s="14" t="n"/>
+      <c r="S87" s="14" t="n"/>
+      <c r="T87" s="14" t="n"/>
+      <c r="U87" s="14" t="n"/>
+      <c r="V87" s="14" t="n"/>
+      <c r="W87" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X87" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y87" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z87" s="14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA87" s="13" t="inlineStr">
+        <is>
+          <t>Aggregate only actual ZedBoard producer inputs. Unsupported or unavailable details remain explicit as NotAvailable/BadNotSupported and are never synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>SDR</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>Aggregate quality of SDR acquisition.</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>nsu=urn:fnal:gizmo;s=GIZMo.Health.SDR</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I88" s="14" t="n"/>
+      <c r="J88" s="14" t="n"/>
+      <c r="K88" s="14" t="n"/>
+      <c r="L88" s="14" t="n"/>
+      <c r="M88" s="14" t="n"/>
+      <c r="N88" s="14" t="n"/>
+      <c r="O88" s="14" t="n"/>
+      <c r="P88" s="14" t="n"/>
+      <c r="Q88" s="14" t="n"/>
+      <c r="R88" s="14" t="n"/>
+      <c r="S88" s="14" t="n"/>
+      <c r="T88" s="14" t="n"/>
+      <c r="U88" s="14" t="n"/>
+      <c r="V88" s="14" t="n"/>
+      <c r="W88" s="14" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="X88" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y88" s="14" t="inlineStr">
+        <is>
+          <t>On-Change</t>
+        </is>
+      </c>
+      <c r="Z88" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA88" s="13" t="inlineStr">
+        <is>
+          <t>Aggregate only actual ZedBoard producer inputs. Unsupported or unavailable details remain explicit as NotAvailable/BadNotSupported and are never synthesized.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n"/>
@@ -10803,7 +11417,7 @@
       <c r="AA204" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA75"/>
+  <autoFilter ref="A1:AA88"/>
   <dataValidations count="5">
     <dataValidation sqref="E2:E204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
       <formula1>"Boolean,Byte,Short,Integer,Long,Float,Double,String,DateTime"</formula1>
@@ -10824,8 +11438,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;BLegacy GIZMo — ZedBoard implementation</oddHeader>
-    <oddFooter>&amp;LDraft 0.7 — GIZMo OPC UA-to-Ignition requirements&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;C&amp;BGIZMo Kria — K26 SOM / KR260 implementation</oddHeader>
+    <oddFooter>&amp;LDraft 0.9 — GIZMo OPC UA-to-Ignition requirements&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/deliverables/GIZMo_ZedBoard_DCS_Intake.xlsx
+++ b/deliverables/GIZMo_ZedBoard_DCS_Intake.xlsx
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="B1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>opc.tcp://&lt;assigned-host&gt;:4842 (final production host/IP assigned by Slow Controls)</t>
+          <t>opc.tcp://&lt;assigned-zed-host&gt;:&lt;assigned-port&gt; (distinct from the Kria endpoint; final production assignment by Slow Controls)</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Stable string NodeIds; resolve namespace URI at connection time; do not hard-code namespace index.</t>
+          <t>The generated Kria model 1.3.1 schema is the authoritative GIZMo–Slow Controls contract. Stable string NodeIds, datatypes, units, ranges, access metadata, and meanings are canonical; resolve the namespace URI at connection time and do not hard-code a namespace index. The ZedBoard profile is conforming and non-authoritative.</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Control rows are listed first and color-coded. Green Read-Write rows are bounded configuration setpoints; amber Write-Only rows are typed OPC UA Methods. Read-Only measurement/status rows are device readbacks and must not be writable. Notes identify implemented versus commissioning-gated capabilities.</t>
+          <t>Control rows are listed first and color-coded. Green Read-Write rows are bounded configuration setpoints; amber Write-Only rows are typed OPC UA Methods. Read-Only measurement/status rows are device readbacks. A narrower ZedBoard accepted subset does not change canonical engineering metadata. Notes identify implemented, development, and commissioning-gated capabilities.</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Draft 0.9 requirements intake for joint GIZMo / Slow Controls review</t>
+          <t>Draft 0.10 requirements intake for joint GIZMo / Slow Controls review</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>DUNE-doc 37315 v.1 bridge/OPC UA/Ignition architecture and June 2026 SC infrastructure/status analysis. Ignition reads each GIZMo OPC UA endpoint directly and owns production tags, alarms, trends, audit, and history; no intermediate history service is requested.</t>
+          <t>DUNE-doc 37315 v.1 bridge/OPC UA/Ignition architecture and June 2026 SC infrastructure/status analysis. Ignition uses two independent connections, reads each GIZMo endpoint directly, and owns production tags, alarms, trends, audit, and history. Neither producer is a fallback, proxy, lifecycle owner, or control path for the other; no intermediate history service is requested.</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Kria values use the retained 2026-07-27..2026-08-03 permanent SQLite replica as observational evidence. Legacy values use 15 direct coherent frames from 2026-08-12, 27 contiguous adapter-pilot cycles, and the 2026-08-13 native-server authenticated 100-Ohm idempotent write/readback. The full 100-cycle physical-display acceptance remains open. These sources refine nominal/desired fields but do not replace approved alarm or metrology limits.</t>
+          <t>Kria values use the retained 2026-07-27..2026-08-03 permanent SQLite replica as observational evidence. Legacy values use 15 direct coherent frames from 2026-08-12, 27 contiguous adapter-pilot cycles, and a 2026-08-13 target-side development-server 100-Ohm idempotent transaction. The ZedBoard server remains in development; the 100-cycle physical-display and production-security acceptance gates remain open. Evidence refines nominal/desired fields but does not replace approved alarm or metrology limits.</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>Validated writable legacy alarm threshold.</t>
+          <t>Canonical writable alarm threshold; ZedBoard accepts a hardware-supported subset.</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="19" t="n">
-        <v>1023</v>
+        <v>1000000</v>
       </c>
       <c r="K2" s="19" t="n">
         <v>100</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AA2" s="21" t="inlineStr">
         <is>
-          <t>IMPLEMENTED NATIVE CONTROL. Authenticated OPC UA UInt32 range is 0..1023 Ohm; anonymous writes are denied and the initial normal/operator band is 1..500 Ohm. Requested initial setpoint is 100 Ohm. Each write requires fresh exact controller identity and agreement among journal, persistent file, and live word; it atomically persists the value, updates/readbacks controller memory, sends the recovered display transaction, resumes the same PID, and reports Configuration.LastCommandResult. On 2026-08-13 the native ARMv7 OPC UA server was deployed on the ZedBoard at TCP 4842 with target-local recovery buffering and automatic time synchronization. Anonymous sessions are read-only. An authenticated, idempotent 100-Ohm ThresholdOhm write passed persistent-file, live controller word, recovery-journal, and display-transaction readback without changing the controller or recovery process identity. Other configuration writes and all Methods remain explicitly unsupported.</t>
+          <t>CANONICAL MODEL 1.3.1 METADATA. OPC UA UInt32 is ReadWrite with an engineering range of 0..1,000,000 Ohm. The ZedBoard development implementation accepts only 0..1023 Ohm and shall return BadOutOfRange above 1023; this local capability does not narrow the contract. The initial operator band is 1..500 Ohm and the requested setpoint is 100 Ohm. A target-side 100-Ohm development transaction passed persistent-file, live-word, journal, and display-transaction readback, but production acceptance remains open. Other configuration writes and all Methods are unsupported.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AA3" s="21" t="inlineStr">
         <is>
-          <t>REQUIRED FUTURE CONTROL, COMMISSIONING STAGE 1; the deployed native endpoint does not expose this node and rejects every non-threshold write. OPC UA UInt32 is requested. The live SysV service starts GIZMO.elf with argument 3 and the engineering note documents RUN default 3 seconds. Keep the initial value fixed at 3 until an upper bound, update mechanism, and alternate cadences are commissioned.</t>
+          <t>REQUESTED FUTURE CONTRACT ADDITION, COMMISSIONING STAGE 1. This node is not in authoritative model 1.3.1 and the ZedBoard profile rejects every non-threshold write. The live SysV service starts GIZMO.elf with argument 3; keep the requested value fixed at 3 until a common model addition, upper bound, update mechanism, and alternate cadences are commissioned.</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="AA24" s="13" t="inlineStr">
         <is>
-          <t>IMPLEMENTED MODEL 1.3. Published value: Fermi National Accelerator Laboratory.</t>
+          <t>IMPLEMENTED MODEL 1.3.1. Published value: Fermi National Accelerator Laboratory.</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,11 @@
       </c>
       <c r="I26" s="14" t="n"/>
       <c r="J26" s="14" t="n"/>
-      <c r="K26" s="14" t="n"/>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>urn:fnal:gizmo</t>
+        </is>
+      </c>
       <c r="L26" s="14" t="n"/>
       <c r="M26" s="14" t="n"/>
       <c r="N26" s="14" t="n"/>
@@ -3184,7 +3188,11 @@
       <c r="Z26" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="AA26" s="13" t="inlineStr"/>
+      <c r="AA26" s="13" t="inlineStr">
+        <is>
+          <t>AUTHORITATIVE CONTRACT. Resolve this namespace URI at connection time; never hard-code the runtime namespace index.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
@@ -3229,7 +3237,11 @@
       </c>
       <c r="I27" s="14" t="n"/>
       <c r="J27" s="14" t="n"/>
-      <c r="K27" s="14" t="n"/>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
       <c r="L27" s="14" t="n"/>
       <c r="M27" s="14" t="n"/>
       <c r="N27" s="14" t="n"/>
@@ -3255,7 +3267,11 @@
       <c r="Z27" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="AA27" s="13" t="inlineStr"/>
+      <c r="AA27" s="13" t="inlineStr">
+        <is>
+          <t>AUTHORITATIVE CONTRACT. The Kria-generated model 1.3.1 schema defines the required baseline for both producers.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
@@ -3592,7 +3608,11 @@
       </c>
       <c r="I32" s="14" t="n"/>
       <c r="J32" s="14" t="n"/>
-      <c r="K32" s="14" t="n"/>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00:00Z</t>
+        </is>
+      </c>
       <c r="L32" s="14" t="n"/>
       <c r="M32" s="14" t="n"/>
       <c r="N32" s="14" t="n"/>
@@ -3620,7 +3640,7 @@
       </c>
       <c r="AA32" s="13" t="inlineStr">
         <is>
-          <t>IMPLEMENTED MODEL 1.3. The published model date is 2026-07-27 UTC.</t>
+          <t>AUTHORITATIVE MODEL 1.3.1 publication date.</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3952,7 @@
       </c>
       <c r="AA36" s="13" t="inlineStr">
         <is>
-          <t>Documented legacy presentation range is 0..500 Ohm; values above 500 are HIGH Z. The controller's internal estimate is mathematically clamped at 999 Ohm, but 999 is not a physical span endpoint. The installed CT/inductor calibration is not yet revalidated. The current connected electronics-only setup produced 111.554..111.902 Ohm across 15 coherent completed RUN frames and the screen displayed 112 Ohm/green. Nominal 112 is therefore a dated live observation, not a detector-loop target. The requested finite normal band is 100..500 Ohm; HIGH Z is also normal. Do not configure a second independent ResistanceOhm comparison once authoritative Alarm.Active is available. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits. The deployed read-only adapter then captured 27 contiguous cycles (Sequence 21..47) on 2026-08-13: 111.465703..112.010978 Ohm, mean 111.722419 Ohm, and exactly 100 Ohm threshold; the calculated legacy display-equivalent rounding was 112 Ohm in 26 cycles and 111 Ohm in one. The samples carried UncertainLastUsableValue and Measurement.Quality=Uncertain, consistent with the unvalidated legacy measurement path. Target communication was lost before the requested 100 cycles completed, so this is additional commissioning evidence, not acceptance.</t>
+          <t>Documented legacy presentation range is 0..500 Ohm; values above 500 are HIGH Z. The controller's internal estimate is mathematically clamped at 999 Ohm, but 999 is not a physical span endpoint. The installed CT/inductor calibration is not yet revalidated. The current connected electronics-only setup produced 111.554..111.902 Ohm across 15 coherent completed RUN frames and the screen displayed 112 Ohm/green. Nominal 112 is therefore a dated live observation, not a detector-loop target. The requested finite normal band is 100..500 Ohm; HIGH Z is also normal and carries Good quality with ResistanceRange=OutOfRange and no finite resistance. Do not configure a second independent ResistanceOhm comparison once authoritative Alarm.Active is available. Read-only live ZedBoard sample set on 2026-08-12: 15 coherent completed RUN frames from the unchanged controlled GIZMO.elf. These are observations of the connected commissioning setup, not validated detector-loop limits. The deployed read-only adapter then captured 27 contiguous cycles (Sequence 21..47) on 2026-08-13: 111.465703..112.010978 Ohm, mean 111.722419 Ohm, and exactly 100 Ohm threshold; the calculated legacy display-equivalent rounding was 112 Ohm in 26 cycles and 111 Ohm in one. The samples carried UncertainLastUsableValue and Measurement.Quality=Uncertain, consistent with the unvalidated legacy measurement path. Target communication was lost before the requested 100 cycles completed, so this is additional commissioning evidence, not acceptance.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>1023</v>
+        <v>1000000</v>
       </c>
       <c r="K40" s="14" t="n">
         <v>100</v>
@@ -4254,7 +4274,7 @@
       </c>
       <c r="AA40" s="13" t="inlineStr">
         <is>
-          <t>Live global_th readback was exactly 100 Ohm in every one of 15 coherent completed RUN frames on 2026-08-12, every one of 27 adapter-pilot cycles, and the native-server control acceptance on 2026-08-13. Use 100 Ohm as the requested initial setpoint. The recovered display/controller field and authenticated OPC UA implementation accept UInt32 values 0..1023 Ohm; the initial normal/operator band remains 1..500 Ohm. On 2026-08-13 the native ARMv7 OPC UA server was deployed on the ZedBoard at TCP 4842 with target-local recovery buffering and automatic time synchronization. Anonymous sessions are read-only. An authenticated, idempotent 100-Ohm ThresholdOhm write passed persistent-file, live controller word, recovery-journal, and display-transaction readback without changing the controller or recovery process identity. Other configuration writes and all Methods remain explicitly unsupported.</t>
+          <t>CANONICAL MODEL 1.3.1 readback span is 0..1,000,000 Ohm. The connected legacy controller returned exactly 100 Ohm in 15 coherent frames and 27 adapter-pilot cycles; a target-side development transaction also read back 100 Ohm. The ZedBoard accepted write subset is 0..1023 Ohm and the initial operator band is 1..500 Ohm. These are development observations, not production acceptance.</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5641,7 @@
       </c>
       <c r="AA57" s="15" t="inlineStr">
         <is>
-          <t>The native target server is implemented and deployed. ThresholdOhm is its only authenticated writable variable; requested controls below remain commissioning-gated unless their Notes say implemented. On 2026-08-13 the native ARMv7 OPC UA server was deployed on the ZedBoard at TCP 4842 with target-local recovery buffering and automatic time synchronization. Anonymous sessions are read-only. An authenticated, idempotent 100-Ohm ThresholdOhm write passed persistent-file, live controller word, recovery-journal, and display-transaction readback without changing the controller or recovery process identity. Other configuration writes and all Methods remain explicitly unsupported.</t>
+          <t>DEVELOPMENT VALUE. Publish the version of the independent conforming ZedBoard server. ThresholdOhm is its only candidate authenticated write; other requested controls remain unsupported or commissioning-gated. A target-side build was exercised on 2026-08-13 but is not production accepted.</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5886,7 @@
       </c>
       <c r="AA60" s="13" t="inlineStr">
         <is>
-          <t>Readback, not a second command path. The requested initial value is 100 Ohm. Refresh it from the controller journal after a write and compare Configuration.LastCommandResult. On 2026-08-13 the native ARMv7 OPC UA server was deployed on the ZedBoard at TCP 4842 with target-local recovery buffering and automatic time synchronization. Anonymous sessions are read-only. An authenticated, idempotent 100-Ohm ThresholdOhm write passed persistent-file, live controller word, recovery-journal, and display-transaction readback without changing the controller or recovery process identity. Other configuration writes and all Methods remain explicitly unsupported.</t>
+          <t>Readback, not a second command path. Refresh from the controller journal after a threshold write and compare Configuration.LastCommandResult. The requested initial value is 100 Ohm; the 0..1023 span is a ZedBoard hardware capability, not an override of canonical threshold metadata. Target-side readback is development evidence only.</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6143,7 @@
       </c>
       <c r="AA63" s="13" t="inlineStr">
         <is>
-          <t>IMPLEMENTED for the native threshold transaction and rejection reason. The model-1.4 Operations command-status nodes remain requested future audit/readback additions.</t>
+          <t>DEVELOPMENT READBACK for the bounded threshold transaction and rejection reason. The model-1.4 Operations command-status nodes remain requested future contract additions.</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10995,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;BLegacy GIZMo — ZedBoard implementation</oddHeader>
-    <oddFooter>&amp;LDraft 0.9 — GIZMo OPC UA-to-Ignition requirements&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDraft 0.10 — GIZMo OPC UA-to-Ignition requirements&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
